--- a/預測結果與評估指標_kfold_mask幾何_年齡性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_年齡性別.xlsx
@@ -493,28 +493,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>403.60700000000003</v>
+        <v>405.481</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.056664233630308</v>
+        <v>21.070718003581007</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.9433357663696924</v>
+        <v>-1.9292819964189931</v>
       </c>
       <c r="G2" s="0">
-        <v>1.9433357663696924</v>
+        <v>1.9292819964189931</v>
       </c>
       <c r="H2" s="0">
-        <v>20.556664233630308</v>
+        <v>20.570718003581007</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.4433357663696924</v>
+        <v>-2.4292819964189931</v>
       </c>
       <c r="J2" s="0">
-        <v>2.4433357663696924</v>
+        <v>2.4292819964189931</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -537,28 +537,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.62289999999996</v>
+        <v>605.36530000000005</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.281474168078006</v>
+        <v>21.284933154664618</v>
       </c>
       <c r="F3" s="0">
-        <v>0.28147416807800596</v>
+        <v>0.28493315466461766</v>
       </c>
       <c r="G3" s="0">
-        <v>0.28147416807800596</v>
+        <v>0.28493315466461766</v>
       </c>
       <c r="H3" s="0">
-        <v>20.781474168078006</v>
+        <v>20.784933154664618</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.21852583192199404</v>
+        <v>-0.21506684533538234</v>
       </c>
       <c r="J3" s="0">
-        <v>0.21852583192199404</v>
+        <v>0.21506684533538234</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -581,28 +581,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>773.59109999999998</v>
+        <v>740.86210000000005</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.043666299225126</v>
+        <v>21.043170279592907</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.4563337007748736</v>
+        <v>-2.456829720407093</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4563337007748736</v>
+        <v>2.456829720407093</v>
       </c>
       <c r="H4" s="0">
-        <v>20.543666299225126</v>
+        <v>20.543170279592907</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.9563337007748736</v>
+        <v>-2.956829720407093</v>
       </c>
       <c r="J4" s="0">
-        <v>2.9563337007748736</v>
+        <v>2.956829720407093</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -625,28 +625,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>579.42529999999999</v>
+        <v>580.86249999999996</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.894988968387828</v>
+        <v>20.891499715534245</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.10501103161217173</v>
+        <v>-0.10850028446575521</v>
       </c>
       <c r="G5" s="0">
-        <v>0.10501103161217173</v>
+        <v>0.10850028446575521</v>
       </c>
       <c r="H5" s="0">
-        <v>20.394988968387828</v>
+        <v>20.391499715534245</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.60501103161217174</v>
+        <v>-0.60850028446575522</v>
       </c>
       <c r="J5" s="0">
-        <v>0.60501103161217174</v>
+        <v>0.60850028446575522</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -669,28 +669,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>632.08730000000003</v>
+        <v>620.73389999999995</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.311270124405059</v>
+        <v>21.310692036581507</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.18872987559494092</v>
+        <v>-0.18930796341849288</v>
       </c>
       <c r="G6" s="0">
-        <v>0.18872987559494092</v>
+        <v>0.18930796341849288</v>
       </c>
       <c r="H6" s="0">
-        <v>20.811270124405059</v>
+        <v>20.810692036581507</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.68872987559494092</v>
+        <v>-0.68930796341849288</v>
       </c>
       <c r="J6" s="0">
-        <v>0.68872987559494092</v>
+        <v>0.68930796341849288</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -713,28 +713,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>720.98979999999995</v>
+        <v>711.67399999999998</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.039768188481372</v>
+        <v>21.044565327837137</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.96023181151862858</v>
+        <v>-0.9554346721628626</v>
       </c>
       <c r="G7" s="0">
-        <v>0.96023181151862858</v>
+        <v>0.9554346721628626</v>
       </c>
       <c r="H7" s="0">
-        <v>20.539768188481372</v>
+        <v>20.544565327837137</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.4602318115186286</v>
+        <v>-1.4554346721628626</v>
       </c>
       <c r="J7" s="0">
-        <v>1.4602318115186286</v>
+        <v>1.4554346721628626</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -757,28 +757,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>758.05489999999998</v>
+        <v>757.66719999999998</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.093746555118962</v>
+        <v>21.091512494301433</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.9062534448810382</v>
+        <v>-3.9084875056985666</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9062534448810382</v>
+        <v>3.9084875056985666</v>
       </c>
       <c r="H8" s="0">
-        <v>20.593746555118962</v>
+        <v>20.591512494301433</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.4062534448810382</v>
+        <v>-4.4084875056985666</v>
       </c>
       <c r="J8" s="0">
-        <v>4.4062534448810382</v>
+        <v>4.4084875056985666</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -801,28 +801,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>400.07780000000002</v>
+        <v>390.43310000000002</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.207876044357047</v>
+        <v>21.216272655913208</v>
       </c>
       <c r="F9" s="0">
-        <v>0.70787604435704665</v>
+        <v>0.71627265591320821</v>
       </c>
       <c r="G9" s="0">
-        <v>0.70787604435704665</v>
+        <v>0.71627265591320821</v>
       </c>
       <c r="H9" s="0">
-        <v>20.707876044357047</v>
+        <v>20.716272655913208</v>
       </c>
       <c r="I9" s="0">
-        <v>0.20787604435704665</v>
+        <v>0.21627265591320821</v>
       </c>
       <c r="J9" s="0">
-        <v>0.20787604435704665</v>
+        <v>0.21627265591320821</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>1</v>
@@ -845,28 +845,28 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1283.9973</v>
+        <v>1263.4103</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.567640276620765</v>
+        <v>21.556737030586668</v>
       </c>
       <c r="F10" s="0">
-        <v>0.56764027662076444</v>
+        <v>0.55673703058666746</v>
       </c>
       <c r="G10" s="0">
-        <v>0.56764027662076444</v>
+        <v>0.55673703058666746</v>
       </c>
       <c r="H10" s="0">
-        <v>21.067640276620765</v>
+        <v>21.056737030586668</v>
       </c>
       <c r="I10" s="0">
-        <v>0.067640276620764439</v>
+        <v>0.056737030586667458</v>
       </c>
       <c r="J10" s="0">
-        <v>0.067640276620764439</v>
+        <v>0.056737030586667458</v>
       </c>
       <c r="K10" s="0" t="b">
         <v>1</v>
@@ -889,28 +889,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>317.95030000000003</v>
+        <v>319.74869999999999</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.97367471135199</v>
+        <v>20.978921601907814</v>
       </c>
       <c r="F11" s="0">
-        <v>2.9736747113519897</v>
+        <v>2.978921601907814</v>
       </c>
       <c r="G11" s="0">
-        <v>2.9736747113519897</v>
+        <v>2.978921601907814</v>
       </c>
       <c r="H11" s="0">
-        <v>20.47367471135199</v>
+        <v>20.478921601907814</v>
       </c>
       <c r="I11" s="0">
-        <v>2.4736747113519897</v>
+        <v>2.478921601907814</v>
       </c>
       <c r="J11" s="0">
-        <v>2.4736747113519897</v>
+        <v>2.478921601907814</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -933,28 +933,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>750.11170000000004</v>
+        <v>718.36379999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.57159425235885</v>
+        <v>20.570603014799801</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.4284057476411505</v>
+        <v>-4.4293969852001993</v>
       </c>
       <c r="G12" s="0">
-        <v>4.4284057476411505</v>
+        <v>4.4293969852001993</v>
       </c>
       <c r="H12" s="0">
-        <v>20.07159425235885</v>
+        <v>20.070603014799801</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.9284057476411505</v>
+        <v>-4.9293969852001993</v>
       </c>
       <c r="J12" s="0">
-        <v>4.9284057476411505</v>
+        <v>4.9293969852001993</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -977,28 +977,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>675.26099999999997</v>
+        <v>669.91160000000002</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.572924444786406</v>
+        <v>20.571575403710249</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.9270755552135945</v>
+        <v>-1.9284245962897515</v>
       </c>
       <c r="G13" s="0">
-        <v>1.9270755552135945</v>
+        <v>1.9284245962897515</v>
       </c>
       <c r="H13" s="0">
-        <v>20.072924444786406</v>
+        <v>20.071575403710249</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.4270755552135945</v>
+        <v>-2.4284245962897515</v>
       </c>
       <c r="J13" s="0">
-        <v>2.4270755552135945</v>
+        <v>2.4284245962897515</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1021,28 +1021,28 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>674.45989999999995</v>
+        <v>672.01459999999997</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.042461517179916</v>
+        <v>21.041730360401925</v>
       </c>
       <c r="F14" s="0">
-        <v>0.54246151717991609</v>
+        <v>0.54173036040192457</v>
       </c>
       <c r="G14" s="0">
-        <v>0.54246151717991609</v>
+        <v>0.54173036040192457</v>
       </c>
       <c r="H14" s="0">
-        <v>20.542461517179916</v>
+        <v>20.541730360401925</v>
       </c>
       <c r="I14" s="0">
-        <v>0.042461517179916086</v>
+        <v>0.041730360401924571</v>
       </c>
       <c r="J14" s="0">
-        <v>0.042461517179916086</v>
+        <v>0.041730360401924571</v>
       </c>
       <c r="K14" s="0" t="b">
         <v>1</v>
@@ -1065,28 +1065,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>583.64300000000003</v>
+        <v>585.0598</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>21.003575337074576</v>
+        <v>21.003681466675594</v>
       </c>
       <c r="F15" s="0">
-        <v>1.5035753370745759</v>
+        <v>1.5036814666755944</v>
       </c>
       <c r="G15" s="0">
-        <v>1.5035753370745759</v>
+        <v>1.5036814666755944</v>
       </c>
       <c r="H15" s="0">
-        <v>20.503575337074576</v>
+        <v>20.503681466675594</v>
       </c>
       <c r="I15" s="0">
-        <v>1.0035753370745759</v>
+        <v>1.0036814666755944</v>
       </c>
       <c r="J15" s="0">
-        <v>1.0035753370745759</v>
+        <v>1.0036814666755944</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1109,28 +1109,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>617.06880000000001</v>
+        <v>618.17600000000004</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.612852311500003</v>
+        <v>21.608546133841124</v>
       </c>
       <c r="F16" s="0">
-        <v>2.1128523115000029</v>
+        <v>2.1085461338411235</v>
       </c>
       <c r="G16" s="0">
-        <v>2.1128523115000029</v>
+        <v>2.1085461338411235</v>
       </c>
       <c r="H16" s="0">
-        <v>21.112852311500003</v>
+        <v>21.108546133841124</v>
       </c>
       <c r="I16" s="0">
-        <v>1.6128523115000029</v>
+        <v>1.6085461338411235</v>
       </c>
       <c r="J16" s="0">
-        <v>1.6128523115000029</v>
+        <v>1.6085461338411235</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1153,28 +1153,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1130.2846</v>
+        <v>1122.4987000000001</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>21.043012629685517</v>
+        <v>21.042398949760873</v>
       </c>
       <c r="F17" s="0">
-        <v>2.5430126296855171</v>
+        <v>2.542398949760873</v>
       </c>
       <c r="G17" s="0">
-        <v>2.5430126296855171</v>
+        <v>2.542398949760873</v>
       </c>
       <c r="H17" s="0">
-        <v>20.543012629685517</v>
+        <v>20.542398949760873</v>
       </c>
       <c r="I17" s="0">
-        <v>2.0430126296855171</v>
+        <v>2.042398949760873</v>
       </c>
       <c r="J17" s="0">
-        <v>2.0430126296855171</v>
+        <v>2.042398949760873</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1197,28 +1197,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1452.2846</v>
+        <v>1459.4197999999999</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.559129402206608</v>
+        <v>20.555745108543828</v>
       </c>
       <c r="F18" s="0">
-        <v>-3.190870597793392</v>
+        <v>-3.1942548914561719</v>
       </c>
       <c r="G18" s="0">
-        <v>3.190870597793392</v>
+        <v>3.1942548914561719</v>
       </c>
       <c r="H18" s="0">
-        <v>20.059129402206608</v>
+        <v>20.055745108543828</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.690870597793392</v>
+        <v>-3.6942548914561719</v>
       </c>
       <c r="J18" s="0">
-        <v>3.690870597793392</v>
+        <v>3.6942548914561719</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1241,28 +1241,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>668.60829999999999</v>
+        <v>667.94280000000003</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.044419079495715</v>
+        <v>21.042512279998803</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2055809205042856</v>
+        <v>-1.2074877200011969</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2055809205042856</v>
+        <v>1.2074877200011969</v>
       </c>
       <c r="H19" s="0">
-        <v>20.544419079495715</v>
+        <v>20.542512279998803</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7055809205042856</v>
+        <v>-1.7074877200011969</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7055809205042856</v>
+        <v>1.7074877200011969</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1285,28 +1285,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>750.32280000000003</v>
+        <v>755.404</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.086018990762181</v>
+        <v>21.098399844661458</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.4139810092378191</v>
+        <v>-4.4016001553385422</v>
       </c>
       <c r="G20" s="0">
-        <v>4.4139810092378191</v>
+        <v>4.4016001553385422</v>
       </c>
       <c r="H20" s="0">
-        <v>20.586018990762181</v>
+        <v>20.598399844661458</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.9139810092378191</v>
+        <v>-4.9016001553385422</v>
       </c>
       <c r="J20" s="0">
-        <v>4.9139810092378191</v>
+        <v>4.9016001553385422</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1329,28 +1329,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>345.22919999999999</v>
+        <v>344.29160000000002</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.655838029628214</v>
+        <v>20.656074011089174</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.8441619703717862</v>
+        <v>-1.8439259889108257</v>
       </c>
       <c r="G21" s="0">
-        <v>1.8441619703717862</v>
+        <v>1.8439259889108257</v>
       </c>
       <c r="H21" s="0">
-        <v>20.155838029628214</v>
+        <v>20.156074011089174</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.3441619703717862</v>
+        <v>-2.3439259889108257</v>
       </c>
       <c r="J21" s="0">
-        <v>2.3441619703717862</v>
+        <v>2.3439259889108257</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1373,28 +1373,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>622.22630000000004</v>
+        <v>613.17560000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>21.042474257640837</v>
+        <v>21.041740188558944</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.45752574235916299</v>
+        <v>-0.45825981144105654</v>
       </c>
       <c r="G22" s="0">
-        <v>0.45752574235916299</v>
+        <v>0.45825981144105654</v>
       </c>
       <c r="H22" s="0">
-        <v>20.542474257640837</v>
+        <v>20.541740188558944</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.95752574235916299</v>
+        <v>-0.95825981144105654</v>
       </c>
       <c r="J22" s="0">
-        <v>0.95752574235916299</v>
+        <v>0.95825981144105654</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>671.48209999999995</v>
+        <v>674.47910000000002</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.042879726533357</v>
+        <v>21.04224660827213</v>
       </c>
       <c r="F23" s="0">
-        <v>1.0428797265333571</v>
+        <v>1.04224660827213</v>
       </c>
       <c r="G23" s="0">
-        <v>1.0428797265333571</v>
+        <v>1.04224660827213</v>
       </c>
       <c r="H23" s="0">
-        <v>20.542879726533357</v>
+        <v>20.54224660827213</v>
       </c>
       <c r="I23" s="0">
-        <v>0.54287972653335714</v>
+        <v>0.54224660827213</v>
       </c>
       <c r="J23" s="0">
-        <v>0.54287972653335714</v>
+        <v>0.54224660827213</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1461,28 +1461,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>582.96010000000001</v>
+        <v>577.67240000000004</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.177469992661436</v>
+        <v>21.183477580070232</v>
       </c>
       <c r="F24" s="0">
-        <v>1.677469992661436</v>
+        <v>1.6834775800702317</v>
       </c>
       <c r="G24" s="0">
-        <v>1.677469992661436</v>
+        <v>1.6834775800702317</v>
       </c>
       <c r="H24" s="0">
-        <v>20.677469992661436</v>
+        <v>20.683477580070232</v>
       </c>
       <c r="I24" s="0">
-        <v>1.177469992661436</v>
+        <v>1.1834775800702317</v>
       </c>
       <c r="J24" s="0">
-        <v>1.177469992661436</v>
+        <v>1.1834775800702317</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1505,28 +1505,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.6952</v>
+        <v>577.55370000000005</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.058667188729643</v>
+        <v>21.056678090271152</v>
       </c>
       <c r="F25" s="0">
-        <v>2.5586671887296433</v>
+        <v>2.5566780902711521</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5586671887296433</v>
+        <v>2.5566780902711521</v>
       </c>
       <c r="H25" s="0">
-        <v>20.558667188729643</v>
+        <v>20.556678090271152</v>
       </c>
       <c r="I25" s="0">
-        <v>2.0586671887296433</v>
+        <v>2.0566780902711521</v>
       </c>
       <c r="J25" s="0">
-        <v>2.0586671887296433</v>
+        <v>2.0566780902711521</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1549,28 +1549,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>689.21019999999999</v>
+        <v>688.17229999999995</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.663737590576204</v>
+        <v>20.663343191540044</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.58626240942379582</v>
+        <v>-0.58665680845995638</v>
       </c>
       <c r="G26" s="0">
-        <v>0.58626240942379582</v>
+        <v>0.58665680845995638</v>
       </c>
       <c r="H26" s="0">
-        <v>20.163737590576204</v>
+        <v>20.163343191540044</v>
       </c>
       <c r="I26" s="0">
-        <v>-1.0862624094237958</v>
+        <v>-1.0866568084599564</v>
       </c>
       <c r="J26" s="0">
-        <v>1.0862624094237958</v>
+        <v>1.0866568084599564</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>0</v>
@@ -1593,28 +1593,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>641.4787</v>
+        <v>638.71429999999998</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.042418048353113</v>
+        <v>21.041681083173536</v>
       </c>
       <c r="F27" s="0">
-        <v>1.7924180483531131</v>
+        <v>1.7916810831735361</v>
       </c>
       <c r="G27" s="0">
-        <v>1.7924180483531131</v>
+        <v>1.7916810831735361</v>
       </c>
       <c r="H27" s="0">
-        <v>20.542418048353113</v>
+        <v>20.541681083173536</v>
       </c>
       <c r="I27" s="0">
-        <v>1.2924180483531131</v>
+        <v>1.2916810831735361</v>
       </c>
       <c r="J27" s="0">
-        <v>1.2924180483531131</v>
+        <v>1.2916810831735361</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1637,28 +1637,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>684.71199999999999</v>
+        <v>676.74940000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>20.973690179040993</v>
+        <v>20.974145482810755</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.77630982095900691</v>
+        <v>-0.77585451718924503</v>
       </c>
       <c r="G28" s="0">
-        <v>0.77630982095900691</v>
+        <v>0.77585451718924503</v>
       </c>
       <c r="H28" s="0">
-        <v>20.473690179040993</v>
+        <v>20.474145482810755</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.2763098209590069</v>
+        <v>-1.275854517189245</v>
       </c>
       <c r="J28" s="0">
-        <v>1.2763098209590069</v>
+        <v>1.275854517189245</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1681,28 +1681,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>353.73129999999998</v>
+        <v>354.31049999999999</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.042440062165618</v>
+        <v>21.041704267802043</v>
       </c>
       <c r="F29" s="0">
-        <v>0.29244006216561758</v>
+        <v>0.29170426780204295</v>
       </c>
       <c r="G29" s="0">
-        <v>0.29244006216561758</v>
+        <v>0.29170426780204295</v>
       </c>
       <c r="H29" s="0">
-        <v>20.542440062165618</v>
+        <v>20.541704267802043</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.20755993783438243</v>
+        <v>-0.20829573219795705</v>
       </c>
       <c r="J29" s="0">
-        <v>0.20755993783438243</v>
+        <v>0.20829573219795705</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1725,28 +1725,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.46259999999995</v>
+        <v>683.81759999999997</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.435434281612643</v>
+        <v>21.437050483258336</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.064565718387356697</v>
+        <v>-0.062949516741664269</v>
       </c>
       <c r="G30" s="0">
-        <v>0.064565718387356697</v>
+        <v>0.062949516741664269</v>
       </c>
       <c r="H30" s="0">
-        <v>20.935434281612643</v>
+        <v>20.937050483258336</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.5645657183873567</v>
+        <v>-0.56294951674166427</v>
       </c>
       <c r="J30" s="0">
-        <v>0.5645657183873567</v>
+        <v>0.56294951674166427</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1769,28 +1769,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1356.9842000000001</v>
+        <v>1353.5838000000001</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.758416322462978</v>
+        <v>21.744926831537438</v>
       </c>
       <c r="F31" s="0">
-        <v>2.2584163224629776</v>
+        <v>2.2449268315374376</v>
       </c>
       <c r="G31" s="0">
-        <v>2.2584163224629776</v>
+        <v>2.2449268315374376</v>
       </c>
       <c r="H31" s="0">
-        <v>21.258416322462978</v>
+        <v>21.244926831537438</v>
       </c>
       <c r="I31" s="0">
-        <v>1.7584163224629776</v>
+        <v>1.7449268315374376</v>
       </c>
       <c r="J31" s="0">
-        <v>1.7584163224629776</v>
+        <v>1.7449268315374376</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1813,28 +1813,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1312.2254</v>
+        <v>1324.2094</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.746539674192349</v>
+        <v>21.737518017192787</v>
       </c>
       <c r="F32" s="0">
-        <v>2.2465396741923485</v>
+        <v>2.2375180171927873</v>
       </c>
       <c r="G32" s="0">
-        <v>2.2465396741923485</v>
+        <v>2.2375180171927873</v>
       </c>
       <c r="H32" s="0">
-        <v>21.246539674192349</v>
+        <v>21.237518017192787</v>
       </c>
       <c r="I32" s="0">
-        <v>1.7465396741923485</v>
+        <v>1.7375180171927873</v>
       </c>
       <c r="J32" s="0">
-        <v>1.7465396741923485</v>
+        <v>1.7375180171927873</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1857,28 +1857,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1359.0623000000001</v>
+        <v>1370.5188000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.048595392435736</v>
+        <v>21.045121966528523</v>
       </c>
       <c r="F33" s="0">
-        <v>0.048595392435736073</v>
+        <v>0.045121966528522961</v>
       </c>
       <c r="G33" s="0">
-        <v>0.048595392435736073</v>
+        <v>0.045121966528522961</v>
       </c>
       <c r="H33" s="0">
-        <v>20.548595392435736</v>
+        <v>20.545121966528523</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.45140460756426393</v>
+        <v>-0.45487803347147704</v>
       </c>
       <c r="J33" s="0">
-        <v>0.45140460756426393</v>
+        <v>0.45487803347147704</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>611.02089999999998</v>
+        <v>595.53899999999999</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>21.081737235382107</v>
+        <v>21.082657883092331</v>
       </c>
       <c r="F34" s="0">
-        <v>0.83173723538210709</v>
+        <v>0.83265788309233102</v>
       </c>
       <c r="G34" s="0">
-        <v>0.83173723538210709</v>
+        <v>0.83265788309233102</v>
       </c>
       <c r="H34" s="0">
-        <v>20.581737235382107</v>
+        <v>20.582657883092331</v>
       </c>
       <c r="I34" s="0">
-        <v>0.33173723538210709</v>
+        <v>0.33265788309233102</v>
       </c>
       <c r="J34" s="0">
-        <v>0.33173723538210709</v>
+        <v>0.33265788309233102</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>1</v>
@@ -1945,28 +1945,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>623.09130000000005</v>
+        <v>620.18640000000005</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.054512440512252</v>
+        <v>21.052454294620691</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.44548755948774854</v>
+        <v>-0.4475457053793086</v>
       </c>
       <c r="G35" s="0">
-        <v>0.44548755948774854</v>
+        <v>0.4475457053793086</v>
       </c>
       <c r="H35" s="0">
-        <v>20.554512440512252</v>
+        <v>20.552454294620691</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.94548755948774854</v>
+        <v>-0.9475457053793086</v>
       </c>
       <c r="J35" s="0">
-        <v>0.94548755948774854</v>
+        <v>0.9475457053793086</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1989,28 +1989,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>590.04459999999995</v>
+        <v>589.86860000000001</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.053824223776662</v>
+        <v>21.051911188857915</v>
       </c>
       <c r="F36" s="0">
-        <v>1.5538242237766617</v>
+        <v>1.5519111888579147</v>
       </c>
       <c r="G36" s="0">
-        <v>1.5538242237766617</v>
+        <v>1.5519111888579147</v>
       </c>
       <c r="H36" s="0">
-        <v>20.553824223776662</v>
+        <v>20.551911188857915</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0538242237766617</v>
+        <v>1.0519111888579147</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0538242237766617</v>
+        <v>1.0519111888579147</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2033,28 +2033,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.99620000000004</v>
+        <v>724.63610000000006</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>21.043052801215115</v>
+        <v>21.042450557707717</v>
       </c>
       <c r="F37" s="0">
-        <v>-3.956947198784885</v>
+        <v>-3.957549442292283</v>
       </c>
       <c r="G37" s="0">
-        <v>3.956947198784885</v>
+        <v>3.957549442292283</v>
       </c>
       <c r="H37" s="0">
-        <v>20.543052801215115</v>
+        <v>20.542450557707717</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.456947198784885</v>
+        <v>-4.457549442292283</v>
       </c>
       <c r="J37" s="0">
-        <v>4.456947198784885</v>
+        <v>4.457549442292283</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2077,28 +2077,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>600.44100000000003</v>
+        <v>598.2287</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.970339176244011</v>
+        <v>20.971857664797003</v>
       </c>
       <c r="F38" s="0">
-        <v>1.9703391762440106</v>
+        <v>1.9718576647970032</v>
       </c>
       <c r="G38" s="0">
-        <v>1.9703391762440106</v>
+        <v>1.9718576647970032</v>
       </c>
       <c r="H38" s="0">
-        <v>20.470339176244011</v>
+        <v>20.471857664797003</v>
       </c>
       <c r="I38" s="0">
-        <v>1.4703391762440106</v>
+        <v>1.4718576647970032</v>
       </c>
       <c r="J38" s="0">
-        <v>1.4703391762440106</v>
+        <v>1.4718576647970032</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2121,28 +2121,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>692.81489999999997</v>
+        <v>681.9153</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.435149609211518</v>
+        <v>20.431651717169018</v>
       </c>
       <c r="F39" s="0">
-        <v>1.4351496092115177</v>
+        <v>1.431651717169018</v>
       </c>
       <c r="G39" s="0">
-        <v>1.4351496092115177</v>
+        <v>1.431651717169018</v>
       </c>
       <c r="H39" s="0">
-        <v>19.935149609211518</v>
+        <v>19.931651717169018</v>
       </c>
       <c r="I39" s="0">
-        <v>0.93514960921151769</v>
+        <v>0.93165171716901796</v>
       </c>
       <c r="J39" s="0">
-        <v>0.93514960921151769</v>
+        <v>0.93165171716901796</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2165,28 +2165,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1193.8898999999999</v>
+        <v>1171.8478</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.049824395113085</v>
+        <v>21.053704760706953</v>
       </c>
       <c r="F40" s="0">
-        <v>0.049824395113084563</v>
+        <v>0.053704760706953181</v>
       </c>
       <c r="G40" s="0">
-        <v>0.049824395113084563</v>
+        <v>0.053704760706953181</v>
       </c>
       <c r="H40" s="0">
-        <v>20.549824395113085</v>
+        <v>20.553704760706953</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.45017560488691544</v>
+        <v>-0.44629523929304682</v>
       </c>
       <c r="J40" s="0">
-        <v>0.45017560488691544</v>
+        <v>0.44629523929304682</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2209,28 +2209,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>666.36320000000001</v>
+        <v>665.75360000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.012964306097</v>
+        <v>21.025686562000004</v>
       </c>
       <c r="F41" s="0">
-        <v>0.51296430609700039</v>
+        <v>0.52568656200000419</v>
       </c>
       <c r="G41" s="0">
-        <v>0.51296430609700039</v>
+        <v>0.52568656200000419</v>
       </c>
       <c r="H41" s="0">
-        <v>20.512964306097</v>
+        <v>20.525686562000004</v>
       </c>
       <c r="I41" s="0">
-        <v>0.012964306097000389</v>
+        <v>0.025686562000004187</v>
       </c>
       <c r="J41" s="0">
-        <v>0.012964306097000389</v>
+        <v>0.025686562000004187</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2253,28 +2253,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>340.92939999999999</v>
+        <v>343.99220000000003</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.043013636277632</v>
+        <v>21.04240278361997</v>
       </c>
       <c r="F42" s="0">
-        <v>1.7930136362776317</v>
+        <v>1.7924027836199699</v>
       </c>
       <c r="G42" s="0">
-        <v>1.7930136362776317</v>
+        <v>1.7924027836199699</v>
       </c>
       <c r="H42" s="0">
-        <v>20.543013636277632</v>
+        <v>20.54240278361997</v>
       </c>
       <c r="I42" s="0">
-        <v>1.2930136362776317</v>
+        <v>1.2924027836199699</v>
       </c>
       <c r="J42" s="0">
-        <v>1.2930136362776317</v>
+        <v>1.2924027836199699</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2297,28 +2297,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>582.97400000000005</v>
+        <v>584.32039999999995</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.90169207000072</v>
+        <v>20.8986377703567</v>
       </c>
       <c r="F43" s="0">
-        <v>0.90169207000072049</v>
+        <v>0.89863777035670012</v>
       </c>
       <c r="G43" s="0">
-        <v>0.90169207000072049</v>
+        <v>0.89863777035670012</v>
       </c>
       <c r="H43" s="0">
-        <v>20.40169207000072</v>
+        <v>20.3986377703567</v>
       </c>
       <c r="I43" s="0">
-        <v>0.40169207000072049</v>
+        <v>0.39863777035670012</v>
       </c>
       <c r="J43" s="0">
-        <v>0.40169207000072049</v>
+        <v>0.39863777035670012</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2341,28 +2341,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>657.05769999999996</v>
+        <v>660.15719999999999</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.517830234342593</v>
+        <v>20.515558818811808</v>
       </c>
       <c r="F44" s="0">
-        <v>0.51783023434259334</v>
+        <v>0.5155588188118081</v>
       </c>
       <c r="G44" s="0">
-        <v>0.51783023434259334</v>
+        <v>0.5155588188118081</v>
       </c>
       <c r="H44" s="0">
-        <v>20.017830234342593</v>
+        <v>20.015558818811808</v>
       </c>
       <c r="I44" s="0">
-        <v>0.017830234342593343</v>
+        <v>0.015558818811808095</v>
       </c>
       <c r="J44" s="0">
-        <v>0.017830234342593343</v>
+        <v>0.015558818811808095</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2385,28 +2385,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>584.81910000000005</v>
+        <v>581.95590000000004</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.056265168220815</v>
+        <v>21.054262896740184</v>
       </c>
       <c r="F45" s="0">
-        <v>1.0562651682208149</v>
+        <v>1.0542628967401839</v>
       </c>
       <c r="G45" s="0">
-        <v>1.0562651682208149</v>
+        <v>1.0542628967401839</v>
       </c>
       <c r="H45" s="0">
-        <v>20.556265168220815</v>
+        <v>20.554262896740184</v>
       </c>
       <c r="I45" s="0">
-        <v>0.55626516822081484</v>
+        <v>0.55426289674018392</v>
       </c>
       <c r="J45" s="0">
-        <v>0.55626516822081484</v>
+        <v>0.55426289674018392</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1457.3396</v>
+        <v>1432.1427000000001</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.664007834574854</v>
+        <v>20.66250706690068</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.3359921654251465</v>
+        <v>-1.3374929330993197</v>
       </c>
       <c r="G46" s="0">
-        <v>1.3359921654251465</v>
+        <v>1.3374929330993197</v>
       </c>
       <c r="H46" s="0">
-        <v>20.164007834574854</v>
+        <v>20.16250706690068</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.8359921654251465</v>
+        <v>-1.8374929330993197</v>
       </c>
       <c r="J46" s="0">
-        <v>1.8359921654251465</v>
+        <v>1.8374929330993197</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2473,28 +2473,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1394.6958999999999</v>
+        <v>1393.6792</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.665135309697846</v>
+        <v>20.663286495562641</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.3348646903021546</v>
+        <v>-1.336713504437359</v>
       </c>
       <c r="G47" s="0">
-        <v>1.3348646903021546</v>
+        <v>1.336713504437359</v>
       </c>
       <c r="H47" s="0">
-        <v>20.165135309697846</v>
+        <v>20.163286495562641</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.8348646903021546</v>
+        <v>-1.836713504437359</v>
       </c>
       <c r="J47" s="0">
-        <v>1.8348646903021546</v>
+        <v>1.836713504437359</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1393.5521000000001</v>
+        <v>1418.9514999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.072270684968228</v>
+        <v>21.068436192376822</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.9277293150317725</v>
+        <v>-1.9315638076231778</v>
       </c>
       <c r="G48" s="0">
-        <v>1.9277293150317725</v>
+        <v>1.9315638076231778</v>
       </c>
       <c r="H48" s="0">
-        <v>20.572270684968228</v>
+        <v>20.568436192376822</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.4277293150317725</v>
+        <v>-2.4315638076231778</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4277293150317725</v>
+        <v>2.4315638076231778</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2561,28 +2561,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1328.9452000000001</v>
+        <v>1319.8444999999999</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.062417054921635</v>
+        <v>21.05834123613603</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.68758294507836482</v>
+        <v>-0.69165876386396974</v>
       </c>
       <c r="G49" s="0">
-        <v>0.68758294507836482</v>
+        <v>0.69165876386396974</v>
       </c>
       <c r="H49" s="0">
-        <v>20.562417054921635</v>
+        <v>20.55834123613603</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.1875829450783648</v>
+        <v>-1.1916587638639697</v>
       </c>
       <c r="J49" s="0">
-        <v>1.1875829450783648</v>
+        <v>1.1916587638639697</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2605,28 +2605,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1373.3529000000001</v>
+        <v>1370.9471000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.016874076160086</v>
+        <v>21.012883839083255</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.48312592383991415</v>
+        <v>-0.48711616091674515</v>
       </c>
       <c r="G50" s="0">
-        <v>0.48312592383991415</v>
+        <v>0.48711616091674515</v>
       </c>
       <c r="H50" s="0">
-        <v>20.516874076160086</v>
+        <v>20.512883839083255</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.98312592383991415</v>
+        <v>-0.98711616091674514</v>
       </c>
       <c r="J50" s="0">
-        <v>0.98312592383991415</v>
+        <v>0.98711616091674514</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2649,28 +2649,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1232.3471999999999</v>
+        <v>1230.9086</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.247696034805696</v>
+        <v>21.249556248746877</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0476960348056963</v>
+        <v>2.0495562487468781</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0476960348056963</v>
+        <v>2.0495562487468781</v>
       </c>
       <c r="H51" s="0">
-        <v>20.747696034805696</v>
+        <v>20.749556248746877</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5476960348056963</v>
+        <v>1.5495562487468781</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5476960348056963</v>
+        <v>1.5495562487468781</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2693,28 +2693,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1151.9466</v>
+        <v>1142.3658</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>21.058728599218831</v>
+        <v>21.05516042166439</v>
       </c>
       <c r="F52" s="0">
-        <v>3.5587285992188313</v>
+        <v>3.5551604216643895</v>
       </c>
       <c r="G52" s="0">
-        <v>3.5587285992188313</v>
+        <v>3.5551604216643895</v>
       </c>
       <c r="H52" s="0">
-        <v>20.558728599218831</v>
+        <v>20.55516042166439</v>
       </c>
       <c r="I52" s="0">
-        <v>3.0587285992188313</v>
+        <v>3.0551604216643895</v>
       </c>
       <c r="J52" s="0">
-        <v>3.0587285992188313</v>
+        <v>3.0551604216643895</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2737,28 +2737,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1179.067</v>
+        <v>1183.6578999999999</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>21.042742877951653</v>
+        <v>21.042085512631012</v>
       </c>
       <c r="F53" s="0">
-        <v>2.6427428779516546</v>
+        <v>2.642085512631013</v>
       </c>
       <c r="G53" s="0">
-        <v>2.6427428779516546</v>
+        <v>2.642085512631013</v>
       </c>
       <c r="H53" s="0">
-        <v>20.542742877951653</v>
+        <v>20.542085512631012</v>
       </c>
       <c r="I53" s="0">
-        <v>2.1427428779516546</v>
+        <v>2.142085512631013</v>
       </c>
       <c r="J53" s="0">
-        <v>2.1427428779516546</v>
+        <v>2.142085512631013</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2781,28 +2781,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.4477999999999</v>
+        <v>1127.7965999999999</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>21.000657422099302</v>
+        <v>20.998478140281719</v>
       </c>
       <c r="F54" s="0">
-        <v>2.0006574220993017</v>
+        <v>1.9984781402817191</v>
       </c>
       <c r="G54" s="0">
-        <v>2.0006574220993017</v>
+        <v>1.9984781402817191</v>
       </c>
       <c r="H54" s="0">
-        <v>20.500657422099302</v>
+        <v>20.498478140281719</v>
       </c>
       <c r="I54" s="0">
-        <v>1.5006574220993017</v>
+        <v>1.4984781402817191</v>
       </c>
       <c r="J54" s="0">
-        <v>1.5006574220993017</v>
+        <v>1.4984781402817191</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2825,28 +2825,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.82780000000002</v>
+        <v>600.21460000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>21.018661659833455</v>
+        <v>21.023812055335927</v>
       </c>
       <c r="F55" s="0">
-        <v>1.5186616598334553</v>
+        <v>1.5238120553359274</v>
       </c>
       <c r="G55" s="0">
-        <v>1.5186616598334553</v>
+        <v>1.5238120553359274</v>
       </c>
       <c r="H55" s="0">
-        <v>20.518661659833455</v>
+        <v>20.523812055335927</v>
       </c>
       <c r="I55" s="0">
-        <v>1.0186616598334552</v>
+        <v>1.0238120553359274</v>
       </c>
       <c r="J55" s="0">
-        <v>1.0186616598334552</v>
+        <v>1.0238120553359274</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2869,28 +2869,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>727.90769999999998</v>
+        <v>684.51480000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.776438821163389</v>
+        <v>20.777848617339856</v>
       </c>
       <c r="F56" s="0">
-        <v>0.27643882116338858</v>
+        <v>0.27784861733985622</v>
       </c>
       <c r="G56" s="0">
-        <v>0.27643882116338858</v>
+        <v>0.27784861733985622</v>
       </c>
       <c r="H56" s="0">
-        <v>20.276438821163389</v>
+        <v>20.277848617339856</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.22356117883661142</v>
+        <v>-0.22215138266014378</v>
       </c>
       <c r="J56" s="0">
-        <v>0.22356117883661142</v>
+        <v>0.22215138266014378</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>0</v>
@@ -2913,28 +2913,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>646.02480000000003</v>
+        <v>632.78740000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.067599396673824</v>
+        <v>21.065989215691644</v>
       </c>
       <c r="F57" s="0">
-        <v>0.067599396673823975</v>
+        <v>0.065989215691644176</v>
       </c>
       <c r="G57" s="0">
-        <v>0.067599396673823975</v>
+        <v>0.065989215691644176</v>
       </c>
       <c r="H57" s="0">
-        <v>20.567599396673824</v>
+        <v>20.565989215691644</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.43240060332617603</v>
+        <v>-0.43401078430835582</v>
       </c>
       <c r="J57" s="0">
-        <v>0.43240060332617603</v>
+        <v>0.43401078430835582</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2957,28 +2957,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1120.8548000000001</v>
+        <v>1105.7334000000001</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>21.043029794316592</v>
+        <v>21.042413904615138</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.4569702056834082</v>
+        <v>-2.4575860953848618</v>
       </c>
       <c r="G58" s="0">
-        <v>2.4569702056834082</v>
+        <v>2.4575860953848618</v>
       </c>
       <c r="H58" s="0">
-        <v>20.543029794316592</v>
+        <v>20.542413904615138</v>
       </c>
       <c r="I58" s="0">
-        <v>-2.9569702056834082</v>
+        <v>-2.9575860953848618</v>
       </c>
       <c r="J58" s="0">
-        <v>2.9569702056834082</v>
+        <v>2.9575860953848618</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -3001,28 +3001,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.77250000000004</v>
+        <v>665.27829999999995</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.309949042551267</v>
+        <v>21.315954637397805</v>
       </c>
       <c r="F59" s="0">
-        <v>0.80994904255126698</v>
+        <v>0.81595463739780527</v>
       </c>
       <c r="G59" s="0">
-        <v>0.80994904255126698</v>
+        <v>0.81595463739780527</v>
       </c>
       <c r="H59" s="0">
-        <v>20.809949042551267</v>
+        <v>20.815954637397805</v>
       </c>
       <c r="I59" s="0">
-        <v>0.30994904255126699</v>
+        <v>0.31595463739780527</v>
       </c>
       <c r="J59" s="0">
-        <v>0.30994904255126699</v>
+        <v>0.31595463739780527</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3045,28 +3045,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>695.50199999999995</v>
+        <v>655.14710000000002</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>20.981467447347708</v>
+        <v>20.9841619381891</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.51853255265229237</v>
+        <v>-0.51583806181089997</v>
       </c>
       <c r="G60" s="0">
-        <v>0.51853255265229237</v>
+        <v>0.51583806181089997</v>
       </c>
       <c r="H60" s="0">
-        <v>20.481467447347708</v>
+        <v>20.4841619381891</v>
       </c>
       <c r="I60" s="0">
-        <v>-1.0185325526522924</v>
+        <v>-1.0158380618109</v>
       </c>
       <c r="J60" s="0">
-        <v>1.0185325526522924</v>
+        <v>1.0158380618109</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3089,28 +3089,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>639.4633</v>
+        <v>642.19590000000005</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>21.042438846389469</v>
+        <v>21.041706676248435</v>
       </c>
       <c r="F61" s="0">
-        <v>1.0424388463894694</v>
+        <v>1.0417066762484346</v>
       </c>
       <c r="G61" s="0">
-        <v>1.0424388463894694</v>
+        <v>1.0417066762484346</v>
       </c>
       <c r="H61" s="0">
-        <v>20.542438846389469</v>
+        <v>20.541706676248435</v>
       </c>
       <c r="I61" s="0">
-        <v>0.54243884638946938</v>
+        <v>0.54170667624843461</v>
       </c>
       <c r="J61" s="0">
-        <v>0.54243884638946938</v>
+        <v>0.54170667624843461</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3133,28 +3133,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>699.43420000000003</v>
+        <v>671.02829999999995</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.042570828866534</v>
+        <v>21.041842687338736</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.9574291711334659</v>
+        <v>-1.9581573126612639</v>
       </c>
       <c r="G62" s="0">
-        <v>1.9574291711334659</v>
+        <v>1.9581573126612639</v>
       </c>
       <c r="H62" s="0">
-        <v>20.542570828866534</v>
+        <v>20.541842687338736</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.4574291711334659</v>
+        <v>-2.4581573126612639</v>
       </c>
       <c r="J62" s="0">
-        <v>2.4574291711334659</v>
+        <v>2.4581573126612639</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3177,28 +3177,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>683.36609999999996</v>
+        <v>658.74609999999996</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.101822523591284</v>
+        <v>21.102922757856305</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.39817747640871559</v>
+        <v>-0.39707724214369478</v>
       </c>
       <c r="G63" s="0">
-        <v>0.39817747640871559</v>
+        <v>0.39707724214369478</v>
       </c>
       <c r="H63" s="0">
-        <v>20.601822523591284</v>
+        <v>20.602922757856305</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.89817747640871559</v>
+        <v>-0.89707724214369478</v>
       </c>
       <c r="J63" s="0">
-        <v>0.89817747640871559</v>
+        <v>0.89707724214369478</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3221,28 +3221,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>421.81869999999998</v>
+        <v>418.81540000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.982703192822044</v>
+        <v>20.987135162311674</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.5172968071779565</v>
+        <v>-1.5128648376883263</v>
       </c>
       <c r="G64" s="0">
-        <v>1.5172968071779565</v>
+        <v>1.5128648376883263</v>
       </c>
       <c r="H64" s="0">
-        <v>20.482703192822044</v>
+        <v>20.487135162311674</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.0172968071779565</v>
+        <v>-2.0128648376883263</v>
       </c>
       <c r="J64" s="0">
-        <v>2.0172968071779565</v>
+        <v>2.0128648376883263</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3265,28 +3265,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>594.92830000000004</v>
+        <v>593.42259999999999</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.155276805900662</v>
+        <v>21.166861627534502</v>
       </c>
       <c r="F65" s="0">
-        <v>1.9052768059006624</v>
+        <v>1.9168616275345016</v>
       </c>
       <c r="G65" s="0">
-        <v>1.9052768059006624</v>
+        <v>1.9168616275345016</v>
       </c>
       <c r="H65" s="0">
-        <v>20.655276805900662</v>
+        <v>20.666861627534502</v>
       </c>
       <c r="I65" s="0">
-        <v>1.4052768059006624</v>
+        <v>1.4168616275345016</v>
       </c>
       <c r="J65" s="0">
-        <v>1.4052768059006624</v>
+        <v>1.4168616275345016</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3309,28 +3309,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>672.91949999999997</v>
+        <v>709.44029999999998</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.049602587139844</v>
+        <v>21.048236627444428</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4503974128601556</v>
+        <v>-2.4517633725555719</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4503974128601556</v>
+        <v>2.4517633725555719</v>
       </c>
       <c r="H66" s="0">
-        <v>20.549602587139844</v>
+        <v>20.548236627444428</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9503974128601556</v>
+        <v>-2.9517633725555719</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9503974128601556</v>
+        <v>2.9517633725555719</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3353,28 +3353,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>637.33479999999997</v>
+        <v>625.83199999999999</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.048862012622426</v>
+        <v>21.046739821717004</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.45113798737757449</v>
+        <v>-0.4532601782829957</v>
       </c>
       <c r="G67" s="0">
-        <v>0.45113798737757449</v>
+        <v>0.4532601782829957</v>
       </c>
       <c r="H67" s="0">
-        <v>20.548862012622426</v>
+        <v>20.546739821717004</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.95113798737757449</v>
+        <v>-0.9532601782829957</v>
       </c>
       <c r="J67" s="0">
-        <v>0.95113798737757449</v>
+        <v>0.9532601782829957</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3397,28 +3397,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>879.03800000000001</v>
+        <v>889.9828</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.077561806045718</v>
+        <v>21.075592832838694</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0775618060457184</v>
+        <v>2.0755928328386943</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0775618060457184</v>
+        <v>2.0755928328386943</v>
       </c>
       <c r="H68" s="0">
-        <v>20.577561806045718</v>
+        <v>20.575592832838694</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5775618060457184</v>
+        <v>1.5755928328386943</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5775618060457184</v>
+        <v>1.5755928328386943</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3479,16 +3479,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.496</v>
+        <v>1.494</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8520000000000001</v>
+        <v>1.8500000000000001</v>
       </c>
       <c r="D2" s="0">
-        <v>0.035999999999999997</v>
+        <v>0.035000000000000003</v>
       </c>
       <c r="E2" s="0">
-        <v>0.045999999999999999</v>
+        <v>0.042999999999999997</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3498,19 +3498,19 @@
         <v>86</v>
       </c>
       <c r="B3" s="0">
-        <v>0.012999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="C3" s="0">
-        <v>0.021999999999999999</v>
+        <v>0.023</v>
       </c>
       <c r="D3" s="0">
-        <v>0.010999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="E3" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="F3" s="0">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G3" s="0">
         <v>1.1000000000000001</v>
@@ -3532,12 +3532,12 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.508</v>
+        <v>1.5069999999999999</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.45400000000000001</v>
+        <v>-0.45700000000000002</v>
       </c>
       <c r="F5" s="0">
         <v>38.200000000000003</v>
@@ -3551,10 +3551,10 @@
         <v>89</v>
       </c>
       <c r="B6" s="0">
-        <v>1.526</v>
+        <v>1.5289999999999999</v>
       </c>
       <c r="C6" s="0">
-        <v>1.8959999999999999</v>
+        <v>1.8979999999999999</v>
       </c>
       <c r="D6" s="0">
         <v>0.002</v>
@@ -3570,7 +3570,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.573</v>
+        <v>1.575</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -3691,13 +3691,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>21.334</v>
+        <v>21.355</v>
       </c>
       <c r="C2" s="0">
-        <v>0.82130000000000003</v>
+        <v>0.82020000000000004</v>
       </c>
       <c r="D2" s="0">
-        <v>25.975999999999999</v>
+        <v>26.035</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3714,10 +3714,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.59199999999999997</v>
+        <v>0.55600000000000005</v>
       </c>
       <c r="E3" s="0">
-        <v>0.55620000000000003</v>
+        <v>0.57989999999999997</v>
       </c>
     </row>
     <row r="4">
@@ -3725,16 +3725,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.021700000000000001</v>
+        <v>-0.021600000000000001</v>
       </c>
       <c r="C4" s="0">
         <v>0.013299999999999999</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.631</v>
+        <v>-1.629</v>
       </c>
       <c r="E4" s="0">
-        <v>0.1079</v>
+        <v>0.10829999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -3742,16 +3742,16 @@
         <v>115</v>
       </c>
       <c r="B5" s="0">
-        <v>0.54630000000000001</v>
+        <v>0.54559999999999997</v>
       </c>
       <c r="C5" s="0">
-        <v>0.45400000000000001</v>
+        <v>0.45450000000000002</v>
       </c>
       <c r="D5" s="0">
-        <v>1.2030000000000001</v>
+        <v>1.2010000000000001</v>
       </c>
       <c r="E5" s="0">
-        <v>0.2334</v>
+        <v>0.2344</v>
       </c>
     </row>
   </sheetData>

--- a/預測結果與評估指標_kfold_mask幾何_年齡性別.xlsx
+++ b/預測結果與評估指標_kfold_mask幾何_年齡性別.xlsx
@@ -430,7 +430,7 @@
     <col min="3" max="3" width="13.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.42578125" customWidth="true"/>
+    <col min="6" max="6" width="13.7109375" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="17" customWidth="true"/>
     <col min="9" max="9" width="20.5703125" customWidth="true"/>
@@ -493,28 +493,28 @@
         <v>69</v>
       </c>
       <c r="C2" s="0">
-        <v>405.481</v>
+        <v>408.47719999999998</v>
       </c>
       <c r="D2" s="0">
         <v>23</v>
       </c>
       <c r="E2" s="0">
-        <v>21.070718003581007</v>
+        <v>20.859435521371413</v>
       </c>
       <c r="F2" s="0">
-        <v>-1.9292819964189931</v>
+        <v>-2.1405644786285869</v>
       </c>
       <c r="G2" s="0">
-        <v>1.9292819964189931</v>
+        <v>2.1405644786285869</v>
       </c>
       <c r="H2" s="0">
-        <v>20.570718003581007</v>
+        <v>20.359435521371413</v>
       </c>
       <c r="I2" s="0">
-        <v>-2.4292819964189931</v>
+        <v>-2.6405644786285869</v>
       </c>
       <c r="J2" s="0">
-        <v>2.4292819964189931</v>
+        <v>2.6405644786285869</v>
       </c>
       <c r="K2" s="0" t="b">
         <v>0</v>
@@ -537,28 +537,28 @@
         <v>69</v>
       </c>
       <c r="C3" s="0">
-        <v>605.36530000000005</v>
+        <v>618.74630000000002</v>
       </c>
       <c r="D3" s="0">
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>21.284933154664618</v>
+        <v>21.249665551711526</v>
       </c>
       <c r="F3" s="0">
-        <v>0.28493315466461766</v>
+        <v>0.24966555171152649</v>
       </c>
       <c r="G3" s="0">
-        <v>0.28493315466461766</v>
+        <v>0.24966555171152649</v>
       </c>
       <c r="H3" s="0">
-        <v>20.784933154664618</v>
+        <v>20.749665551711526</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.21506684533538234</v>
+        <v>-0.25033444828847351</v>
       </c>
       <c r="J3" s="0">
-        <v>0.21506684533538234</v>
+        <v>0.25033444828847351</v>
       </c>
       <c r="K3" s="0" t="b">
         <v>0</v>
@@ -581,28 +581,28 @@
         <v>69</v>
       </c>
       <c r="C4" s="0">
-        <v>740.86210000000005</v>
+        <v>757.2885</v>
       </c>
       <c r="D4" s="0">
         <v>23.5</v>
       </c>
       <c r="E4" s="0">
-        <v>21.043170279592907</v>
+        <v>21.100511959484351</v>
       </c>
       <c r="F4" s="0">
-        <v>-2.456829720407093</v>
+        <v>-2.3994880405156493</v>
       </c>
       <c r="G4" s="0">
-        <v>2.456829720407093</v>
+        <v>2.3994880405156493</v>
       </c>
       <c r="H4" s="0">
-        <v>20.543170279592907</v>
+        <v>20.600511959484351</v>
       </c>
       <c r="I4" s="0">
-        <v>-2.956829720407093</v>
+        <v>-2.8994880405156493</v>
       </c>
       <c r="J4" s="0">
-        <v>2.956829720407093</v>
+        <v>2.8994880405156493</v>
       </c>
       <c r="K4" s="0" t="b">
         <v>0</v>
@@ -625,28 +625,28 @@
         <v>69</v>
       </c>
       <c r="C5" s="0">
-        <v>580.86249999999996</v>
+        <v>583.17809999999997</v>
       </c>
       <c r="D5" s="0">
         <v>21</v>
       </c>
       <c r="E5" s="0">
-        <v>20.891499715534245</v>
+        <v>20.712401815151708</v>
       </c>
       <c r="F5" s="0">
-        <v>-0.10850028446575521</v>
+        <v>-0.28759818484829225</v>
       </c>
       <c r="G5" s="0">
-        <v>0.10850028446575521</v>
+        <v>0.28759818484829225</v>
       </c>
       <c r="H5" s="0">
-        <v>20.391499715534245</v>
+        <v>20.212401815151708</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.60850028446575522</v>
+        <v>-0.78759818484829225</v>
       </c>
       <c r="J5" s="0">
-        <v>0.60850028446575522</v>
+        <v>0.78759818484829225</v>
       </c>
       <c r="K5" s="0" t="b">
         <v>0</v>
@@ -669,28 +669,28 @@
         <v>69</v>
       </c>
       <c r="C6" s="0">
-        <v>620.73389999999995</v>
+        <v>633.10580000000004</v>
       </c>
       <c r="D6" s="0">
         <v>21.5</v>
       </c>
       <c r="E6" s="0">
-        <v>21.310692036581507</v>
+        <v>21.260451014603646</v>
       </c>
       <c r="F6" s="0">
-        <v>-0.18930796341849288</v>
+        <v>-0.23954898539635394</v>
       </c>
       <c r="G6" s="0">
-        <v>0.18930796341849288</v>
+        <v>0.23954898539635394</v>
       </c>
       <c r="H6" s="0">
-        <v>20.810692036581507</v>
+        <v>20.760451014603646</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.68930796341849288</v>
+        <v>-0.73954898539635394</v>
       </c>
       <c r="J6" s="0">
-        <v>0.68930796341849288</v>
+        <v>0.73954898539635394</v>
       </c>
       <c r="K6" s="0" t="b">
         <v>0</v>
@@ -713,28 +713,28 @@
         <v>69</v>
       </c>
       <c r="C7" s="0">
-        <v>711.67399999999998</v>
+        <v>712.21130000000005</v>
       </c>
       <c r="D7" s="0">
         <v>22</v>
       </c>
       <c r="E7" s="0">
-        <v>21.044565327837137</v>
+        <v>20.888942594254448</v>
       </c>
       <c r="F7" s="0">
-        <v>-0.9554346721628626</v>
+        <v>-1.1110574057455516</v>
       </c>
       <c r="G7" s="0">
-        <v>0.9554346721628626</v>
+        <v>1.1110574057455516</v>
       </c>
       <c r="H7" s="0">
-        <v>20.544565327837137</v>
+        <v>20.388942594254448</v>
       </c>
       <c r="I7" s="0">
-        <v>-1.4554346721628626</v>
+        <v>-1.6110574057455516</v>
       </c>
       <c r="J7" s="0">
-        <v>1.4554346721628626</v>
+        <v>1.6110574057455516</v>
       </c>
       <c r="K7" s="0" t="b">
         <v>0</v>
@@ -757,28 +757,28 @@
         <v>69</v>
       </c>
       <c r="C8" s="0">
-        <v>757.66719999999998</v>
+        <v>765.37739999999997</v>
       </c>
       <c r="D8" s="0">
         <v>25</v>
       </c>
       <c r="E8" s="0">
-        <v>21.091512494301433</v>
+        <v>20.937720434673015</v>
       </c>
       <c r="F8" s="0">
-        <v>-3.9084875056985666</v>
+        <v>-4.0622795653269854</v>
       </c>
       <c r="G8" s="0">
-        <v>3.9084875056985666</v>
+        <v>4.0622795653269854</v>
       </c>
       <c r="H8" s="0">
-        <v>20.591512494301433</v>
+        <v>20.437720434673015</v>
       </c>
       <c r="I8" s="0">
-        <v>-4.4084875056985666</v>
+        <v>-4.5622795653269854</v>
       </c>
       <c r="J8" s="0">
-        <v>4.4084875056985666</v>
+        <v>4.5622795653269854</v>
       </c>
       <c r="K8" s="0" t="b">
         <v>0</v>
@@ -801,28 +801,28 @@
         <v>69</v>
       </c>
       <c r="C9" s="0">
-        <v>390.43310000000002</v>
+        <v>384.85610000000003</v>
       </c>
       <c r="D9" s="0">
         <v>20.5</v>
       </c>
       <c r="E9" s="0">
-        <v>21.216272655913208</v>
+        <v>21.272526126635448</v>
       </c>
       <c r="F9" s="0">
-        <v>0.71627265591320821</v>
+        <v>0.77252612663544795</v>
       </c>
       <c r="G9" s="0">
-        <v>0.71627265591320821</v>
+        <v>0.77252612663544795</v>
       </c>
       <c r="H9" s="0">
-        <v>20.716272655913208</v>
+        <v>20.772526126635448</v>
       </c>
       <c r="I9" s="0">
-        <v>0.21627265591320821</v>
+        <v>0.27252612663544795</v>
       </c>
       <c r="J9" s="0">
-        <v>0.21627265591320821</v>
+        <v>0.27252612663544795</v>
       </c>
       <c r="K9" s="0" t="b">
         <v>1</v>
@@ -845,31 +845,31 @@
         <v>69</v>
       </c>
       <c r="C10" s="0">
-        <v>1263.4103</v>
+        <v>1296.7855999999999</v>
       </c>
       <c r="D10" s="0">
         <v>21</v>
       </c>
       <c r="E10" s="0">
-        <v>21.556737030586668</v>
+        <v>21.434855124910467</v>
       </c>
       <c r="F10" s="0">
-        <v>0.55673703058666746</v>
+        <v>0.43485512491046663</v>
       </c>
       <c r="G10" s="0">
-        <v>0.55673703058666746</v>
+        <v>0.43485512491046663</v>
       </c>
       <c r="H10" s="0">
-        <v>21.056737030586668</v>
+        <v>20.934855124910467</v>
       </c>
       <c r="I10" s="0">
-        <v>0.056737030586667458</v>
+        <v>-0.065144875089533372</v>
       </c>
       <c r="J10" s="0">
-        <v>0.056737030586667458</v>
+        <v>0.065144875089533372</v>
       </c>
       <c r="K10" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="0">
         <v>2</v>
@@ -889,28 +889,28 @@
         <v>69</v>
       </c>
       <c r="C11" s="0">
-        <v>319.74869999999999</v>
+        <v>320.06220000000002</v>
       </c>
       <c r="D11" s="0">
         <v>18</v>
       </c>
       <c r="E11" s="0">
-        <v>20.978921601907814</v>
+        <v>20.80060391284572</v>
       </c>
       <c r="F11" s="0">
-        <v>2.978921601907814</v>
+        <v>2.8006039128457196</v>
       </c>
       <c r="G11" s="0">
-        <v>2.978921601907814</v>
+        <v>2.8006039128457196</v>
       </c>
       <c r="H11" s="0">
-        <v>20.478921601907814</v>
+        <v>20.30060391284572</v>
       </c>
       <c r="I11" s="0">
-        <v>2.478921601907814</v>
+        <v>2.3006039128457196</v>
       </c>
       <c r="J11" s="0">
-        <v>2.478921601907814</v>
+        <v>2.3006039128457196</v>
       </c>
       <c r="K11" s="0" t="b">
         <v>1</v>
@@ -933,28 +933,28 @@
         <v>69</v>
       </c>
       <c r="C12" s="0">
-        <v>718.36379999999997</v>
+        <v>747.66359999999997</v>
       </c>
       <c r="D12" s="0">
         <v>25</v>
       </c>
       <c r="E12" s="0">
-        <v>20.570603014799801</v>
+        <v>20.640633432339367</v>
       </c>
       <c r="F12" s="0">
-        <v>-4.4293969852001993</v>
+        <v>-4.3593665676606328</v>
       </c>
       <c r="G12" s="0">
-        <v>4.4293969852001993</v>
+        <v>4.3593665676606328</v>
       </c>
       <c r="H12" s="0">
-        <v>20.070603014799801</v>
+        <v>20.140633432339367</v>
       </c>
       <c r="I12" s="0">
-        <v>-4.9293969852001993</v>
+        <v>-4.8593665676606328</v>
       </c>
       <c r="J12" s="0">
-        <v>4.9293969852001993</v>
+        <v>4.8593665676606328</v>
       </c>
       <c r="K12" s="0" t="b">
         <v>0</v>
@@ -977,28 +977,28 @@
         <v>69</v>
       </c>
       <c r="C13" s="0">
-        <v>669.91160000000002</v>
+        <v>659.65279999999996</v>
       </c>
       <c r="D13" s="0">
         <v>22.5</v>
       </c>
       <c r="E13" s="0">
-        <v>20.571575403710249</v>
+        <v>20.642409317495641</v>
       </c>
       <c r="F13" s="0">
-        <v>-1.9284245962897515</v>
+        <v>-1.8575906825043589</v>
       </c>
       <c r="G13" s="0">
-        <v>1.9284245962897515</v>
+        <v>1.8575906825043589</v>
       </c>
       <c r="H13" s="0">
-        <v>20.071575403710249</v>
+        <v>20.142409317495641</v>
       </c>
       <c r="I13" s="0">
-        <v>-2.4284245962897515</v>
+        <v>-2.3575906825043589</v>
       </c>
       <c r="J13" s="0">
-        <v>2.4284245962897515</v>
+        <v>2.3575906825043589</v>
       </c>
       <c r="K13" s="0" t="b">
         <v>0</v>
@@ -1021,31 +1021,31 @@
         <v>69</v>
       </c>
       <c r="C14" s="0">
-        <v>672.01459999999997</v>
+        <v>682.95950000000005</v>
       </c>
       <c r="D14" s="0">
         <v>20.5</v>
       </c>
       <c r="E14" s="0">
-        <v>21.041730360401925</v>
+        <v>20.979559829715029</v>
       </c>
       <c r="F14" s="0">
-        <v>0.54173036040192457</v>
+        <v>0.4795598297150292</v>
       </c>
       <c r="G14" s="0">
-        <v>0.54173036040192457</v>
+        <v>0.4795598297150292</v>
       </c>
       <c r="H14" s="0">
-        <v>20.541730360401925</v>
+        <v>20.479559829715029</v>
       </c>
       <c r="I14" s="0">
-        <v>0.041730360401924571</v>
+        <v>-0.020440170284970804</v>
       </c>
       <c r="J14" s="0">
-        <v>0.041730360401924571</v>
+        <v>0.020440170284970804</v>
       </c>
       <c r="K14" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="0">
         <v>4</v>
@@ -1065,28 +1065,28 @@
         <v>69</v>
       </c>
       <c r="C15" s="0">
-        <v>585.0598</v>
+        <v>587.81489999999997</v>
       </c>
       <c r="D15" s="0">
         <v>19.5</v>
       </c>
       <c r="E15" s="0">
-        <v>21.003681466675594</v>
+        <v>21.000279044702204</v>
       </c>
       <c r="F15" s="0">
-        <v>1.5036814666755944</v>
+        <v>1.5002790447022036</v>
       </c>
       <c r="G15" s="0">
-        <v>1.5036814666755944</v>
+        <v>1.5002790447022036</v>
       </c>
       <c r="H15" s="0">
-        <v>20.503681466675594</v>
+        <v>20.500279044702204</v>
       </c>
       <c r="I15" s="0">
-        <v>1.0036814666755944</v>
+        <v>1.0002790447022036</v>
       </c>
       <c r="J15" s="0">
-        <v>1.0036814666755944</v>
+        <v>1.0002790447022036</v>
       </c>
       <c r="K15" s="0" t="b">
         <v>1</v>
@@ -1109,28 +1109,28 @@
         <v>69</v>
       </c>
       <c r="C16" s="0">
-        <v>618.17600000000004</v>
+        <v>624.73410000000001</v>
       </c>
       <c r="D16" s="0">
         <v>19.5</v>
       </c>
       <c r="E16" s="0">
-        <v>21.608546133841124</v>
+        <v>21.440019631621418</v>
       </c>
       <c r="F16" s="0">
-        <v>2.1085461338411235</v>
+        <v>1.9400196316214178</v>
       </c>
       <c r="G16" s="0">
-        <v>2.1085461338411235</v>
+        <v>1.9400196316214178</v>
       </c>
       <c r="H16" s="0">
-        <v>21.108546133841124</v>
+        <v>20.940019631621418</v>
       </c>
       <c r="I16" s="0">
-        <v>1.6085461338411235</v>
+        <v>1.4400196316214178</v>
       </c>
       <c r="J16" s="0">
-        <v>1.6085461338411235</v>
+        <v>1.4400196316214178</v>
       </c>
       <c r="K16" s="0" t="b">
         <v>1</v>
@@ -1153,28 +1153,28 @@
         <v>69</v>
       </c>
       <c r="C17" s="0">
-        <v>1122.4987000000001</v>
+        <v>1128.8182999999999</v>
       </c>
       <c r="D17" s="0">
         <v>18.5</v>
       </c>
       <c r="E17" s="0">
-        <v>21.042398949760873</v>
+        <v>21.053441567890566</v>
       </c>
       <c r="F17" s="0">
-        <v>2.542398949760873</v>
+        <v>2.553441567890566</v>
       </c>
       <c r="G17" s="0">
-        <v>2.542398949760873</v>
+        <v>2.553441567890566</v>
       </c>
       <c r="H17" s="0">
-        <v>20.542398949760873</v>
+        <v>20.553441567890566</v>
       </c>
       <c r="I17" s="0">
-        <v>2.042398949760873</v>
+        <v>2.053441567890566</v>
       </c>
       <c r="J17" s="0">
-        <v>2.042398949760873</v>
+        <v>2.053441567890566</v>
       </c>
       <c r="K17" s="0" t="b">
         <v>1</v>
@@ -1197,28 +1197,28 @@
         <v>69</v>
       </c>
       <c r="C18" s="0">
-        <v>1459.4197999999999</v>
+        <v>1473.3333</v>
       </c>
       <c r="D18" s="0">
         <v>23.75</v>
       </c>
       <c r="E18" s="0">
-        <v>20.555745108543828</v>
+        <v>20.626004218896888</v>
       </c>
       <c r="F18" s="0">
-        <v>-3.1942548914561719</v>
+        <v>-3.1239957811031118</v>
       </c>
       <c r="G18" s="0">
-        <v>3.1942548914561719</v>
+        <v>3.1239957811031118</v>
       </c>
       <c r="H18" s="0">
-        <v>20.055745108543828</v>
+        <v>20.126004218896888</v>
       </c>
       <c r="I18" s="0">
-        <v>-3.6942548914561719</v>
+        <v>-3.6239957811031118</v>
       </c>
       <c r="J18" s="0">
-        <v>3.6942548914561719</v>
+        <v>3.6239957811031118</v>
       </c>
       <c r="K18" s="0" t="b">
         <v>0</v>
@@ -1241,28 +1241,28 @@
         <v>69</v>
       </c>
       <c r="C19" s="0">
-        <v>667.94280000000003</v>
+        <v>676.57719999999995</v>
       </c>
       <c r="D19" s="0">
         <v>22.25</v>
       </c>
       <c r="E19" s="0">
-        <v>21.042512279998803</v>
+        <v>20.813275538198038</v>
       </c>
       <c r="F19" s="0">
-        <v>-1.2074877200011969</v>
+        <v>-1.4367244618019619</v>
       </c>
       <c r="G19" s="0">
-        <v>1.2074877200011969</v>
+        <v>1.4367244618019619</v>
       </c>
       <c r="H19" s="0">
-        <v>20.542512279998803</v>
+        <v>20.313275538198038</v>
       </c>
       <c r="I19" s="0">
-        <v>-1.7074877200011969</v>
+        <v>-1.9367244618019619</v>
       </c>
       <c r="J19" s="0">
-        <v>1.7074877200011969</v>
+        <v>1.9367244618019619</v>
       </c>
       <c r="K19" s="0" t="b">
         <v>0</v>
@@ -1285,28 +1285,28 @@
         <v>69</v>
       </c>
       <c r="C20" s="0">
-        <v>755.404</v>
+        <v>752.55830000000003</v>
       </c>
       <c r="D20" s="0">
         <v>25.5</v>
       </c>
       <c r="E20" s="0">
-        <v>21.098399844661458</v>
+        <v>20.902928741551776</v>
       </c>
       <c r="F20" s="0">
-        <v>-4.4016001553385422</v>
+        <v>-4.5970712584482243</v>
       </c>
       <c r="G20" s="0">
-        <v>4.4016001553385422</v>
+        <v>4.5970712584482243</v>
       </c>
       <c r="H20" s="0">
-        <v>20.598399844661458</v>
+        <v>20.402928741551776</v>
       </c>
       <c r="I20" s="0">
-        <v>-4.9016001553385422</v>
+        <v>-5.0970712584482243</v>
       </c>
       <c r="J20" s="0">
-        <v>4.9016001553385422</v>
+        <v>5.0970712584482243</v>
       </c>
       <c r="K20" s="0" t="b">
         <v>0</v>
@@ -1329,28 +1329,28 @@
         <v>69</v>
       </c>
       <c r="C21" s="0">
-        <v>344.29160000000002</v>
+        <v>349.81529999999998</v>
       </c>
       <c r="D21" s="0">
         <v>22.5</v>
       </c>
       <c r="E21" s="0">
-        <v>20.656074011089174</v>
+        <v>20.708388171878401</v>
       </c>
       <c r="F21" s="0">
-        <v>-1.8439259889108257</v>
+        <v>-1.7916118281215994</v>
       </c>
       <c r="G21" s="0">
-        <v>1.8439259889108257</v>
+        <v>1.7916118281215994</v>
       </c>
       <c r="H21" s="0">
-        <v>20.156074011089174</v>
+        <v>20.208388171878401</v>
       </c>
       <c r="I21" s="0">
-        <v>-2.3439259889108257</v>
+        <v>-2.2916118281215994</v>
       </c>
       <c r="J21" s="0">
-        <v>2.3439259889108257</v>
+        <v>2.2916118281215994</v>
       </c>
       <c r="K21" s="0" t="b">
         <v>0</v>
@@ -1373,28 +1373,28 @@
         <v>69</v>
       </c>
       <c r="C22" s="0">
-        <v>613.17560000000003</v>
+        <v>617.12260000000003</v>
       </c>
       <c r="D22" s="0">
         <v>21.5</v>
       </c>
       <c r="E22" s="0">
-        <v>21.041740188558944</v>
+        <v>20.977051851551437</v>
       </c>
       <c r="F22" s="0">
-        <v>-0.45825981144105654</v>
+        <v>-0.52294814844856319</v>
       </c>
       <c r="G22" s="0">
-        <v>0.45825981144105654</v>
+        <v>0.52294814844856319</v>
       </c>
       <c r="H22" s="0">
-        <v>20.541740188558944</v>
+        <v>20.477051851551437</v>
       </c>
       <c r="I22" s="0">
-        <v>-0.95825981144105654</v>
+        <v>-1.0229481484485632</v>
       </c>
       <c r="J22" s="0">
-        <v>0.95825981144105654</v>
+        <v>1.0229481484485632</v>
       </c>
       <c r="K22" s="0" t="b">
         <v>0</v>
@@ -1417,28 +1417,28 @@
         <v>69</v>
       </c>
       <c r="C23" s="0">
-        <v>674.47910000000002</v>
+        <v>669.44370000000004</v>
       </c>
       <c r="D23" s="0">
         <v>20</v>
       </c>
       <c r="E23" s="0">
-        <v>21.04224660827213</v>
+        <v>20.957344561221159</v>
       </c>
       <c r="F23" s="0">
-        <v>1.04224660827213</v>
+        <v>0.9573445612211593</v>
       </c>
       <c r="G23" s="0">
-        <v>1.04224660827213</v>
+        <v>0.9573445612211593</v>
       </c>
       <c r="H23" s="0">
-        <v>20.54224660827213</v>
+        <v>20.457344561221159</v>
       </c>
       <c r="I23" s="0">
-        <v>0.54224660827213</v>
+        <v>0.4573445612211593</v>
       </c>
       <c r="J23" s="0">
-        <v>0.54224660827213</v>
+        <v>0.4573445612211593</v>
       </c>
       <c r="K23" s="0" t="b">
         <v>1</v>
@@ -1461,28 +1461,28 @@
         <v>69</v>
       </c>
       <c r="C24" s="0">
-        <v>577.67240000000004</v>
+        <v>584.04089999999997</v>
       </c>
       <c r="D24" s="0">
         <v>19.5</v>
       </c>
       <c r="E24" s="0">
-        <v>21.183477580070232</v>
+        <v>21.20650278708322</v>
       </c>
       <c r="F24" s="0">
-        <v>1.6834775800702317</v>
+        <v>1.7065027870832204</v>
       </c>
       <c r="G24" s="0">
-        <v>1.6834775800702317</v>
+        <v>1.7065027870832204</v>
       </c>
       <c r="H24" s="0">
-        <v>20.683477580070232</v>
+        <v>20.70650278708322</v>
       </c>
       <c r="I24" s="0">
-        <v>1.1834775800702317</v>
+        <v>1.2065027870832203</v>
       </c>
       <c r="J24" s="0">
-        <v>1.1834775800702317</v>
+        <v>1.2065027870832203</v>
       </c>
       <c r="K24" s="0" t="b">
         <v>1</v>
@@ -1505,28 +1505,28 @@
         <v>69</v>
       </c>
       <c r="C25" s="0">
-        <v>577.55370000000005</v>
+        <v>583.09950000000003</v>
       </c>
       <c r="D25" s="0">
         <v>18.5</v>
       </c>
       <c r="E25" s="0">
-        <v>21.056678090271152</v>
+        <v>20.882154163507913</v>
       </c>
       <c r="F25" s="0">
-        <v>2.5566780902711521</v>
+        <v>2.3821541635079129</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5566780902711521</v>
+        <v>2.3821541635079129</v>
       </c>
       <c r="H25" s="0">
-        <v>20.556678090271152</v>
+        <v>20.382154163507913</v>
       </c>
       <c r="I25" s="0">
-        <v>2.0566780902711521</v>
+        <v>1.8821541635079129</v>
       </c>
       <c r="J25" s="0">
-        <v>2.0566780902711521</v>
+        <v>1.8821541635079129</v>
       </c>
       <c r="K25" s="0" t="b">
         <v>1</v>
@@ -1549,28 +1549,28 @@
         <v>69</v>
       </c>
       <c r="C26" s="0">
-        <v>688.17229999999995</v>
+        <v>694.29290000000003</v>
       </c>
       <c r="D26" s="0">
         <v>21.25</v>
       </c>
       <c r="E26" s="0">
-        <v>20.663343191540044</v>
+        <v>20.712281040645991</v>
       </c>
       <c r="F26" s="0">
-        <v>-0.58665680845995638</v>
+        <v>-0.53771895935400948</v>
       </c>
       <c r="G26" s="0">
-        <v>0.58665680845995638</v>
+        <v>0.53771895935400948</v>
       </c>
       <c r="H26" s="0">
-        <v>20.163343191540044</v>
+        <v>20.212281040645991</v>
       </c>
       <c r="I26" s="0">
-        <v>-1.0866568084599564</v>
+        <v>-1.0377189593540095</v>
       </c>
       <c r="J26" s="0">
-        <v>1.0866568084599564</v>
+        <v>1.0377189593540095</v>
       </c>
       <c r="K26" s="0" t="b">
         <v>0</v>
@@ -1593,28 +1593,28 @@
         <v>69</v>
       </c>
       <c r="C27" s="0">
-        <v>638.71429999999998</v>
+        <v>645.69730000000004</v>
       </c>
       <c r="D27" s="0">
         <v>19.25</v>
       </c>
       <c r="E27" s="0">
-        <v>21.041681083173536</v>
+        <v>20.910938068606814</v>
       </c>
       <c r="F27" s="0">
-        <v>1.7916810831735361</v>
+        <v>1.6609380686068143</v>
       </c>
       <c r="G27" s="0">
-        <v>1.7916810831735361</v>
+        <v>1.6609380686068143</v>
       </c>
       <c r="H27" s="0">
-        <v>20.541681083173536</v>
+        <v>20.410938068606814</v>
       </c>
       <c r="I27" s="0">
-        <v>1.2916810831735361</v>
+        <v>1.1609380686068143</v>
       </c>
       <c r="J27" s="0">
-        <v>1.2916810831735361</v>
+        <v>1.1609380686068143</v>
       </c>
       <c r="K27" s="0" t="b">
         <v>1</v>
@@ -1637,28 +1637,28 @@
         <v>69</v>
       </c>
       <c r="C28" s="0">
-        <v>676.74940000000004</v>
+        <v>704.87890000000004</v>
       </c>
       <c r="D28" s="0">
         <v>21.75</v>
       </c>
       <c r="E28" s="0">
-        <v>20.974145482810755</v>
+        <v>20.811432682824751</v>
       </c>
       <c r="F28" s="0">
-        <v>-0.77585451718924503</v>
+        <v>-0.93856731717524866</v>
       </c>
       <c r="G28" s="0">
-        <v>0.77585451718924503</v>
+        <v>0.93856731717524866</v>
       </c>
       <c r="H28" s="0">
-        <v>20.474145482810755</v>
+        <v>20.311432682824751</v>
       </c>
       <c r="I28" s="0">
-        <v>-1.275854517189245</v>
+        <v>-1.4385673171752487</v>
       </c>
       <c r="J28" s="0">
-        <v>1.275854517189245</v>
+        <v>1.4385673171752487</v>
       </c>
       <c r="K28" s="0" t="b">
         <v>0</v>
@@ -1681,28 +1681,28 @@
         <v>69</v>
       </c>
       <c r="C29" s="0">
-        <v>354.31049999999999</v>
+        <v>353.71350000000001</v>
       </c>
       <c r="D29" s="0">
         <v>20.75</v>
       </c>
       <c r="E29" s="0">
-        <v>21.041704267802043</v>
+        <v>20.962394359437955</v>
       </c>
       <c r="F29" s="0">
-        <v>0.29170426780204295</v>
+        <v>0.21239435943795471</v>
       </c>
       <c r="G29" s="0">
-        <v>0.29170426780204295</v>
+        <v>0.21239435943795471</v>
       </c>
       <c r="H29" s="0">
-        <v>20.541704267802043</v>
+        <v>20.462394359437955</v>
       </c>
       <c r="I29" s="0">
-        <v>-0.20829573219795705</v>
+        <v>-0.28760564056204529</v>
       </c>
       <c r="J29" s="0">
-        <v>0.20829573219795705</v>
+        <v>0.28760564056204529</v>
       </c>
       <c r="K29" s="0" t="b">
         <v>0</v>
@@ -1725,28 +1725,28 @@
         <v>69</v>
       </c>
       <c r="C30" s="0">
-        <v>683.81759999999997</v>
+        <v>688.96929999999998</v>
       </c>
       <c r="D30" s="0">
         <v>21.5</v>
       </c>
       <c r="E30" s="0">
-        <v>21.437050483258336</v>
+        <v>21.370450906581709</v>
       </c>
       <c r="F30" s="0">
-        <v>-0.062949516741664269</v>
+        <v>-0.1295490934182908</v>
       </c>
       <c r="G30" s="0">
-        <v>0.062949516741664269</v>
+        <v>0.1295490934182908</v>
       </c>
       <c r="H30" s="0">
-        <v>20.937050483258336</v>
+        <v>20.870450906581709</v>
       </c>
       <c r="I30" s="0">
-        <v>-0.56294951674166427</v>
+        <v>-0.6295490934182908</v>
       </c>
       <c r="J30" s="0">
-        <v>0.56294951674166427</v>
+        <v>0.6295490934182908</v>
       </c>
       <c r="K30" s="0" t="b">
         <v>0</v>
@@ -1769,28 +1769,28 @@
         <v>69</v>
       </c>
       <c r="C31" s="0">
-        <v>1353.5838000000001</v>
+        <v>1374.7736</v>
       </c>
       <c r="D31" s="0">
         <v>19.5</v>
       </c>
       <c r="E31" s="0">
-        <v>21.744926831537438</v>
+        <v>21.51276089319586</v>
       </c>
       <c r="F31" s="0">
-        <v>2.2449268315374376</v>
+        <v>2.0127608931958605</v>
       </c>
       <c r="G31" s="0">
-        <v>2.2449268315374376</v>
+        <v>2.0127608931958605</v>
       </c>
       <c r="H31" s="0">
-        <v>21.244926831537438</v>
+        <v>21.01276089319586</v>
       </c>
       <c r="I31" s="0">
-        <v>1.7449268315374376</v>
+        <v>1.5127608931958605</v>
       </c>
       <c r="J31" s="0">
-        <v>1.7449268315374376</v>
+        <v>1.5127608931958605</v>
       </c>
       <c r="K31" s="0" t="b">
         <v>1</v>
@@ -1813,28 +1813,28 @@
         <v>69</v>
       </c>
       <c r="C32" s="0">
-        <v>1324.2094</v>
+        <v>1328.4146000000001</v>
       </c>
       <c r="D32" s="0">
         <v>19.5</v>
       </c>
       <c r="E32" s="0">
-        <v>21.737518017192787</v>
+        <v>21.50701429963291</v>
       </c>
       <c r="F32" s="0">
-        <v>2.2375180171927873</v>
+        <v>2.0070142996329103</v>
       </c>
       <c r="G32" s="0">
-        <v>2.2375180171927873</v>
+        <v>2.0070142996329103</v>
       </c>
       <c r="H32" s="0">
-        <v>21.237518017192787</v>
+        <v>21.00701429963291</v>
       </c>
       <c r="I32" s="0">
-        <v>1.7375180171927873</v>
+        <v>1.5070142996329103</v>
       </c>
       <c r="J32" s="0">
-        <v>1.7375180171927873</v>
+        <v>1.5070142996329103</v>
       </c>
       <c r="K32" s="0" t="b">
         <v>1</v>
@@ -1857,28 +1857,28 @@
         <v>69</v>
       </c>
       <c r="C33" s="0">
-        <v>1370.5188000000001</v>
+        <v>1401.6427000000001</v>
       </c>
       <c r="D33" s="0">
         <v>21</v>
       </c>
       <c r="E33" s="0">
-        <v>21.045121966528523</v>
+        <v>20.770096139435218</v>
       </c>
       <c r="F33" s="0">
-        <v>0.045121966528522961</v>
+        <v>-0.22990386056478229</v>
       </c>
       <c r="G33" s="0">
-        <v>0.045121966528522961</v>
+        <v>0.22990386056478229</v>
       </c>
       <c r="H33" s="0">
-        <v>20.545121966528523</v>
+        <v>20.270096139435218</v>
       </c>
       <c r="I33" s="0">
-        <v>-0.45487803347147704</v>
+        <v>-0.72990386056478229</v>
       </c>
       <c r="J33" s="0">
-        <v>0.45487803347147704</v>
+        <v>0.72990386056478229</v>
       </c>
       <c r="K33" s="0" t="b">
         <v>0</v>
@@ -1901,28 +1901,28 @@
         <v>69</v>
       </c>
       <c r="C34" s="0">
-        <v>595.53899999999999</v>
+        <v>604.36569999999995</v>
       </c>
       <c r="D34" s="0">
         <v>20.25</v>
       </c>
       <c r="E34" s="0">
-        <v>21.082657883092331</v>
+        <v>21.060283796647322</v>
       </c>
       <c r="F34" s="0">
-        <v>0.83265788309233102</v>
+        <v>0.81028379664732242</v>
       </c>
       <c r="G34" s="0">
-        <v>0.83265788309233102</v>
+        <v>0.81028379664732242</v>
       </c>
       <c r="H34" s="0">
-        <v>20.582657883092331</v>
+        <v>20.560283796647322</v>
       </c>
       <c r="I34" s="0">
-        <v>0.33265788309233102</v>
+        <v>0.31028379664732242</v>
       </c>
       <c r="J34" s="0">
-        <v>0.33265788309233102</v>
+        <v>0.31028379664732242</v>
       </c>
       <c r="K34" s="0" t="b">
         <v>1</v>
@@ -1945,28 +1945,28 @@
         <v>69</v>
       </c>
       <c r="C35" s="0">
-        <v>620.18640000000005</v>
+        <v>621.61170000000004</v>
       </c>
       <c r="D35" s="0">
         <v>21.5</v>
       </c>
       <c r="E35" s="0">
-        <v>21.052454294620691</v>
+        <v>20.86036480306765</v>
       </c>
       <c r="F35" s="0">
-        <v>-0.4475457053793086</v>
+        <v>-0.63963519693234971</v>
       </c>
       <c r="G35" s="0">
-        <v>0.4475457053793086</v>
+        <v>0.63963519693234971</v>
       </c>
       <c r="H35" s="0">
-        <v>20.552454294620691</v>
+        <v>20.36036480306765</v>
       </c>
       <c r="I35" s="0">
-        <v>-0.9475457053793086</v>
+        <v>-1.1396351969323497</v>
       </c>
       <c r="J35" s="0">
-        <v>0.9475457053793086</v>
+        <v>1.1396351969323497</v>
       </c>
       <c r="K35" s="0" t="b">
         <v>0</v>
@@ -1989,28 +1989,28 @@
         <v>69</v>
       </c>
       <c r="C36" s="0">
-        <v>589.86860000000001</v>
+        <v>597.18910000000005</v>
       </c>
       <c r="D36" s="0">
         <v>19.5</v>
       </c>
       <c r="E36" s="0">
-        <v>21.051911188857915</v>
+        <v>20.860366136668056</v>
       </c>
       <c r="F36" s="0">
-        <v>1.5519111888579147</v>
+        <v>1.3603661366680555</v>
       </c>
       <c r="G36" s="0">
-        <v>1.5519111888579147</v>
+        <v>1.3603661366680555</v>
       </c>
       <c r="H36" s="0">
-        <v>20.551911188857915</v>
+        <v>20.360366136668056</v>
       </c>
       <c r="I36" s="0">
-        <v>1.0519111888579147</v>
+        <v>0.8603661366680555</v>
       </c>
       <c r="J36" s="0">
-        <v>1.0519111888579147</v>
+        <v>0.8603661366680555</v>
       </c>
       <c r="K36" s="0" t="b">
         <v>1</v>
@@ -2033,28 +2033,28 @@
         <v>69</v>
       </c>
       <c r="C37" s="0">
-        <v>724.63610000000006</v>
+        <v>738.8483</v>
       </c>
       <c r="D37" s="0">
         <v>25</v>
       </c>
       <c r="E37" s="0">
-        <v>21.042450557707717</v>
+        <v>21.041244430515118</v>
       </c>
       <c r="F37" s="0">
-        <v>-3.957549442292283</v>
+        <v>-3.9587555694848824</v>
       </c>
       <c r="G37" s="0">
-        <v>3.957549442292283</v>
+        <v>3.9587555694848824</v>
       </c>
       <c r="H37" s="0">
-        <v>20.542450557707717</v>
+        <v>20.541244430515118</v>
       </c>
       <c r="I37" s="0">
-        <v>-4.457549442292283</v>
+        <v>-4.4587555694848824</v>
       </c>
       <c r="J37" s="0">
-        <v>4.457549442292283</v>
+        <v>4.4587555694848824</v>
       </c>
       <c r="K37" s="0" t="b">
         <v>0</v>
@@ -2077,28 +2077,28 @@
         <v>69</v>
       </c>
       <c r="C38" s="0">
-        <v>598.2287</v>
+        <v>595.78989999999999</v>
       </c>
       <c r="D38" s="0">
         <v>19</v>
       </c>
       <c r="E38" s="0">
-        <v>20.971857664797003</v>
+        <v>20.802753689003712</v>
       </c>
       <c r="F38" s="0">
-        <v>1.9718576647970032</v>
+        <v>1.8027536890037119</v>
       </c>
       <c r="G38" s="0">
-        <v>1.9718576647970032</v>
+        <v>1.8027536890037119</v>
       </c>
       <c r="H38" s="0">
-        <v>20.471857664797003</v>
+        <v>20.302753689003712</v>
       </c>
       <c r="I38" s="0">
-        <v>1.4718576647970032</v>
+        <v>1.3027536890037119</v>
       </c>
       <c r="J38" s="0">
-        <v>1.4718576647970032</v>
+        <v>1.3027536890037119</v>
       </c>
       <c r="K38" s="0" t="b">
         <v>1</v>
@@ -2121,28 +2121,28 @@
         <v>69</v>
       </c>
       <c r="C39" s="0">
-        <v>681.9153</v>
+        <v>698.92719999999997</v>
       </c>
       <c r="D39" s="0">
         <v>19</v>
       </c>
       <c r="E39" s="0">
-        <v>20.431651717169018</v>
+        <v>20.534089476575552</v>
       </c>
       <c r="F39" s="0">
-        <v>1.431651717169018</v>
+        <v>1.5340894765755522</v>
       </c>
       <c r="G39" s="0">
-        <v>1.431651717169018</v>
+        <v>1.5340894765755522</v>
       </c>
       <c r="H39" s="0">
-        <v>19.931651717169018</v>
+        <v>20.034089476575552</v>
       </c>
       <c r="I39" s="0">
-        <v>0.93165171716901796</v>
+        <v>1.0340894765755522</v>
       </c>
       <c r="J39" s="0">
-        <v>0.93165171716901796</v>
+        <v>1.0340894765755522</v>
       </c>
       <c r="K39" s="0" t="b">
         <v>1</v>
@@ -2165,28 +2165,28 @@
         <v>69</v>
       </c>
       <c r="C40" s="0">
-        <v>1171.8478</v>
+        <v>1170.2615000000001</v>
       </c>
       <c r="D40" s="0">
         <v>21</v>
       </c>
       <c r="E40" s="0">
-        <v>21.053704760706953</v>
+        <v>21.163975507399187</v>
       </c>
       <c r="F40" s="0">
-        <v>0.053704760706953181</v>
+        <v>0.16397550739918643</v>
       </c>
       <c r="G40" s="0">
-        <v>0.053704760706953181</v>
+        <v>0.16397550739918643</v>
       </c>
       <c r="H40" s="0">
-        <v>20.553704760706953</v>
+        <v>20.663975507399187</v>
       </c>
       <c r="I40" s="0">
-        <v>-0.44629523929304682</v>
+        <v>-0.33602449260081357</v>
       </c>
       <c r="J40" s="0">
-        <v>0.44629523929304682</v>
+        <v>0.33602449260081357</v>
       </c>
       <c r="K40" s="0" t="b">
         <v>0</v>
@@ -2209,28 +2209,28 @@
         <v>69</v>
       </c>
       <c r="C41" s="0">
-        <v>665.75360000000001</v>
+        <v>672.51900000000001</v>
       </c>
       <c r="D41" s="0">
         <v>20.5</v>
       </c>
       <c r="E41" s="0">
-        <v>21.025686562000004</v>
+        <v>21.143533875834965</v>
       </c>
       <c r="F41" s="0">
-        <v>0.52568656200000419</v>
+        <v>0.64353387583496513</v>
       </c>
       <c r="G41" s="0">
-        <v>0.52568656200000419</v>
+        <v>0.64353387583496513</v>
       </c>
       <c r="H41" s="0">
-        <v>20.525686562000004</v>
+        <v>20.643533875834965</v>
       </c>
       <c r="I41" s="0">
-        <v>0.025686562000004187</v>
+        <v>0.14353387583496513</v>
       </c>
       <c r="J41" s="0">
-        <v>0.025686562000004187</v>
+        <v>0.14353387583496513</v>
       </c>
       <c r="K41" s="0" t="b">
         <v>1</v>
@@ -2253,28 +2253,28 @@
         <v>69</v>
       </c>
       <c r="C42" s="0">
-        <v>343.99220000000003</v>
+        <v>344.02600000000001</v>
       </c>
       <c r="D42" s="0">
         <v>19.25</v>
       </c>
       <c r="E42" s="0">
-        <v>21.04240278361997</v>
+        <v>21.01928267247003</v>
       </c>
       <c r="F42" s="0">
-        <v>1.7924027836199699</v>
+        <v>1.7692826724700304</v>
       </c>
       <c r="G42" s="0">
-        <v>1.7924027836199699</v>
+        <v>1.7692826724700304</v>
       </c>
       <c r="H42" s="0">
-        <v>20.54240278361997</v>
+        <v>20.51928267247003</v>
       </c>
       <c r="I42" s="0">
-        <v>1.2924027836199699</v>
+        <v>1.2692826724700304</v>
       </c>
       <c r="J42" s="0">
-        <v>1.2924027836199699</v>
+        <v>1.2692826724700304</v>
       </c>
       <c r="K42" s="0" t="b">
         <v>1</v>
@@ -2297,28 +2297,28 @@
         <v>69</v>
       </c>
       <c r="C43" s="0">
-        <v>584.32039999999995</v>
+        <v>585.99260000000004</v>
       </c>
       <c r="D43" s="0">
         <v>20</v>
       </c>
       <c r="E43" s="0">
-        <v>20.8986377703567</v>
+        <v>20.72043609792906</v>
       </c>
       <c r="F43" s="0">
-        <v>0.89863777035670012</v>
+        <v>0.72043609792905983</v>
       </c>
       <c r="G43" s="0">
-        <v>0.89863777035670012</v>
+        <v>0.72043609792905983</v>
       </c>
       <c r="H43" s="0">
-        <v>20.3986377703567</v>
+        <v>20.22043609792906</v>
       </c>
       <c r="I43" s="0">
-        <v>0.39863777035670012</v>
+        <v>0.22043609792905983</v>
       </c>
       <c r="J43" s="0">
-        <v>0.39863777035670012</v>
+        <v>0.22043609792905983</v>
       </c>
       <c r="K43" s="0" t="b">
         <v>1</v>
@@ -2341,28 +2341,28 @@
         <v>69</v>
       </c>
       <c r="C44" s="0">
-        <v>660.15719999999999</v>
+        <v>661.50829999999996</v>
       </c>
       <c r="D44" s="0">
         <v>20</v>
       </c>
       <c r="E44" s="0">
-        <v>20.515558818811808</v>
+        <v>20.599188001341588</v>
       </c>
       <c r="F44" s="0">
-        <v>0.5155588188118081</v>
+        <v>0.59918800134158801</v>
       </c>
       <c r="G44" s="0">
-        <v>0.5155588188118081</v>
+        <v>0.59918800134158801</v>
       </c>
       <c r="H44" s="0">
-        <v>20.015558818811808</v>
+        <v>20.099188001341588</v>
       </c>
       <c r="I44" s="0">
-        <v>0.015558818811808095</v>
+        <v>0.099188001341588006</v>
       </c>
       <c r="J44" s="0">
-        <v>0.015558818811808095</v>
+        <v>0.099188001341588006</v>
       </c>
       <c r="K44" s="0" t="b">
         <v>1</v>
@@ -2385,28 +2385,28 @@
         <v>69</v>
       </c>
       <c r="C45" s="0">
-        <v>581.95590000000004</v>
+        <v>579.78219999999999</v>
       </c>
       <c r="D45" s="0">
         <v>20</v>
       </c>
       <c r="E45" s="0">
-        <v>21.054262896740184</v>
+        <v>20.87125991326586</v>
       </c>
       <c r="F45" s="0">
-        <v>1.0542628967401839</v>
+        <v>0.87125991326585961</v>
       </c>
       <c r="G45" s="0">
-        <v>1.0542628967401839</v>
+        <v>0.87125991326585961</v>
       </c>
       <c r="H45" s="0">
-        <v>20.554262896740184</v>
+        <v>20.37125991326586</v>
       </c>
       <c r="I45" s="0">
-        <v>0.55426289674018392</v>
+        <v>0.37125991326585961</v>
       </c>
       <c r="J45" s="0">
-        <v>0.55426289674018392</v>
+        <v>0.37125991326585961</v>
       </c>
       <c r="K45" s="0" t="b">
         <v>1</v>
@@ -2429,28 +2429,28 @@
         <v>69</v>
       </c>
       <c r="C46" s="0">
-        <v>1432.1427000000001</v>
+        <v>1450.9502</v>
       </c>
       <c r="D46" s="0">
         <v>22</v>
       </c>
       <c r="E46" s="0">
-        <v>20.66250706690068</v>
+        <v>20.70780323916625</v>
       </c>
       <c r="F46" s="0">
-        <v>-1.3374929330993197</v>
+        <v>-1.2921967608337504</v>
       </c>
       <c r="G46" s="0">
-        <v>1.3374929330993197</v>
+        <v>1.2921967608337504</v>
       </c>
       <c r="H46" s="0">
-        <v>20.16250706690068</v>
+        <v>20.20780323916625</v>
       </c>
       <c r="I46" s="0">
-        <v>-1.8374929330993197</v>
+        <v>-1.7921967608337504</v>
       </c>
       <c r="J46" s="0">
-        <v>1.8374929330993197</v>
+        <v>1.7921967608337504</v>
       </c>
       <c r="K46" s="0" t="b">
         <v>0</v>
@@ -2473,28 +2473,28 @@
         <v>69</v>
       </c>
       <c r="C47" s="0">
-        <v>1393.6792</v>
+        <v>1401.4597000000001</v>
       </c>
       <c r="D47" s="0">
         <v>22</v>
       </c>
       <c r="E47" s="0">
-        <v>20.663286495562641</v>
+        <v>20.708808130237543</v>
       </c>
       <c r="F47" s="0">
-        <v>-1.336713504437359</v>
+        <v>-1.2911918697624571</v>
       </c>
       <c r="G47" s="0">
-        <v>1.336713504437359</v>
+        <v>1.2911918697624571</v>
       </c>
       <c r="H47" s="0">
-        <v>20.163286495562641</v>
+        <v>20.208808130237543</v>
       </c>
       <c r="I47" s="0">
-        <v>-1.836713504437359</v>
+        <v>-1.7911918697624572</v>
       </c>
       <c r="J47" s="0">
-        <v>1.836713504437359</v>
+        <v>1.7911918697624572</v>
       </c>
       <c r="K47" s="0" t="b">
         <v>0</v>
@@ -2517,28 +2517,28 @@
         <v>69</v>
       </c>
       <c r="C48" s="0">
-        <v>1418.9514999999999</v>
+        <v>1394.8155999999999</v>
       </c>
       <c r="D48" s="0">
         <v>23</v>
       </c>
       <c r="E48" s="0">
-        <v>21.068436192376822</v>
+        <v>20.867579196055445</v>
       </c>
       <c r="F48" s="0">
-        <v>-1.9315638076231778</v>
+        <v>-2.1324208039445551</v>
       </c>
       <c r="G48" s="0">
-        <v>1.9315638076231778</v>
+        <v>2.1324208039445551</v>
       </c>
       <c r="H48" s="0">
-        <v>20.568436192376822</v>
+        <v>20.367579196055445</v>
       </c>
       <c r="I48" s="0">
-        <v>-2.4315638076231778</v>
+        <v>-2.6324208039445551</v>
       </c>
       <c r="J48" s="0">
-        <v>2.4315638076231778</v>
+        <v>2.6324208039445551</v>
       </c>
       <c r="K48" s="0" t="b">
         <v>0</v>
@@ -2561,28 +2561,28 @@
         <v>69</v>
       </c>
       <c r="C49" s="0">
-        <v>1319.8444999999999</v>
+        <v>1329.1301000000001</v>
       </c>
       <c r="D49" s="0">
         <v>21.75</v>
       </c>
       <c r="E49" s="0">
-        <v>21.05834123613603</v>
+        <v>20.831305419045592</v>
       </c>
       <c r="F49" s="0">
-        <v>-0.69165876386396974</v>
+        <v>-0.91869458095440848</v>
       </c>
       <c r="G49" s="0">
-        <v>0.69165876386396974</v>
+        <v>0.91869458095440848</v>
       </c>
       <c r="H49" s="0">
-        <v>20.55834123613603</v>
+        <v>20.331305419045592</v>
       </c>
       <c r="I49" s="0">
-        <v>-1.1916587638639697</v>
+        <v>-1.4186945809544085</v>
       </c>
       <c r="J49" s="0">
-        <v>1.1916587638639697</v>
+        <v>1.4186945809544085</v>
       </c>
       <c r="K49" s="0" t="b">
         <v>0</v>
@@ -2605,28 +2605,28 @@
         <v>69</v>
       </c>
       <c r="C50" s="0">
-        <v>1370.9471000000001</v>
+        <v>1378.3186000000001</v>
       </c>
       <c r="D50" s="0">
         <v>21.5</v>
       </c>
       <c r="E50" s="0">
-        <v>21.012883839083255</v>
+        <v>20.878716176021012</v>
       </c>
       <c r="F50" s="0">
-        <v>-0.48711616091674515</v>
+        <v>-0.62128382397898818</v>
       </c>
       <c r="G50" s="0">
-        <v>0.48711616091674515</v>
+        <v>0.62128382397898818</v>
       </c>
       <c r="H50" s="0">
-        <v>20.512883839083255</v>
+        <v>20.378716176021012</v>
       </c>
       <c r="I50" s="0">
-        <v>-0.98711616091674514</v>
+        <v>-1.1212838239789882</v>
       </c>
       <c r="J50" s="0">
-        <v>0.98711616091674514</v>
+        <v>1.1212838239789882</v>
       </c>
       <c r="K50" s="0" t="b">
         <v>0</v>
@@ -2649,28 +2649,28 @@
         <v>69</v>
       </c>
       <c r="C51" s="0">
-        <v>1230.9086</v>
+        <v>1221.2897</v>
       </c>
       <c r="D51" s="0">
         <v>19.199999999999999</v>
       </c>
       <c r="E51" s="0">
-        <v>21.249556248746877</v>
+        <v>21.244528168523473</v>
       </c>
       <c r="F51" s="0">
-        <v>2.0495562487468781</v>
+        <v>2.044528168523474</v>
       </c>
       <c r="G51" s="0">
-        <v>2.0495562487468781</v>
+        <v>2.044528168523474</v>
       </c>
       <c r="H51" s="0">
-        <v>20.749556248746877</v>
+        <v>20.744528168523473</v>
       </c>
       <c r="I51" s="0">
-        <v>1.5495562487468781</v>
+        <v>1.544528168523474</v>
       </c>
       <c r="J51" s="0">
-        <v>1.5495562487468781</v>
+        <v>1.544528168523474</v>
       </c>
       <c r="K51" s="0" t="b">
         <v>1</v>
@@ -2693,28 +2693,28 @@
         <v>69</v>
       </c>
       <c r="C52" s="0">
-        <v>1142.3658</v>
+        <v>1153.4326000000001</v>
       </c>
       <c r="D52" s="0">
         <v>17.5</v>
       </c>
       <c r="E52" s="0">
-        <v>21.05516042166439</v>
+        <v>20.831319504851031</v>
       </c>
       <c r="F52" s="0">
-        <v>3.5551604216643895</v>
+        <v>3.3313195048510309</v>
       </c>
       <c r="G52" s="0">
-        <v>3.5551604216643895</v>
+        <v>3.3313195048510309</v>
       </c>
       <c r="H52" s="0">
-        <v>20.55516042166439</v>
+        <v>20.331319504851031</v>
       </c>
       <c r="I52" s="0">
-        <v>3.0551604216643895</v>
+        <v>2.8313195048510309</v>
       </c>
       <c r="J52" s="0">
-        <v>3.0551604216643895</v>
+        <v>2.8313195048510309</v>
       </c>
       <c r="K52" s="0" t="b">
         <v>1</v>
@@ -2737,28 +2737,28 @@
         <v>69</v>
       </c>
       <c r="C53" s="0">
-        <v>1183.6578999999999</v>
+        <v>1196.1094000000001</v>
       </c>
       <c r="D53" s="0">
         <v>18.399999999999999</v>
       </c>
       <c r="E53" s="0">
-        <v>21.042085512631012</v>
+        <v>20.968100954795496</v>
       </c>
       <c r="F53" s="0">
-        <v>2.642085512631013</v>
+        <v>2.5681009547954972</v>
       </c>
       <c r="G53" s="0">
-        <v>2.642085512631013</v>
+        <v>2.5681009547954972</v>
       </c>
       <c r="H53" s="0">
-        <v>20.542085512631012</v>
+        <v>20.468100954795496</v>
       </c>
       <c r="I53" s="0">
-        <v>2.142085512631013</v>
+        <v>2.0681009547954972</v>
       </c>
       <c r="J53" s="0">
-        <v>2.142085512631013</v>
+        <v>2.0681009547954972</v>
       </c>
       <c r="K53" s="0" t="b">
         <v>1</v>
@@ -2781,28 +2781,28 @@
         <v>69</v>
       </c>
       <c r="C54" s="0">
-        <v>1127.7965999999999</v>
+        <v>1146.1387</v>
       </c>
       <c r="D54" s="0">
         <v>19</v>
       </c>
       <c r="E54" s="0">
-        <v>20.998478140281719</v>
+        <v>20.854637262700429</v>
       </c>
       <c r="F54" s="0">
-        <v>1.9984781402817191</v>
+        <v>1.8546372627004288</v>
       </c>
       <c r="G54" s="0">
-        <v>1.9984781402817191</v>
+        <v>1.8546372627004288</v>
       </c>
       <c r="H54" s="0">
-        <v>20.498478140281719</v>
+        <v>20.354637262700429</v>
       </c>
       <c r="I54" s="0">
-        <v>1.4984781402817191</v>
+        <v>1.3546372627004288</v>
       </c>
       <c r="J54" s="0">
-        <v>1.4984781402817191</v>
+        <v>1.3546372627004288</v>
       </c>
       <c r="K54" s="0" t="b">
         <v>1</v>
@@ -2825,28 +2825,28 @@
         <v>69</v>
       </c>
       <c r="C55" s="0">
-        <v>600.21460000000002</v>
+        <v>610.65390000000002</v>
       </c>
       <c r="D55" s="0">
         <v>19.5</v>
       </c>
       <c r="E55" s="0">
-        <v>21.023812055335927</v>
+        <v>20.862584170233951</v>
       </c>
       <c r="F55" s="0">
-        <v>1.5238120553359274</v>
+        <v>1.3625841702339514</v>
       </c>
       <c r="G55" s="0">
-        <v>1.5238120553359274</v>
+        <v>1.3625841702339514</v>
       </c>
       <c r="H55" s="0">
-        <v>20.523812055335927</v>
+        <v>20.362584170233951</v>
       </c>
       <c r="I55" s="0">
-        <v>1.0238120553359274</v>
+        <v>0.8625841702339514</v>
       </c>
       <c r="J55" s="0">
-        <v>1.0238120553359274</v>
+        <v>0.8625841702339514</v>
       </c>
       <c r="K55" s="0" t="b">
         <v>1</v>
@@ -2869,28 +2869,28 @@
         <v>69</v>
       </c>
       <c r="C56" s="0">
-        <v>684.51480000000004</v>
+        <v>701.03470000000004</v>
       </c>
       <c r="D56" s="0">
         <v>20.5</v>
       </c>
       <c r="E56" s="0">
-        <v>20.777848617339856</v>
+        <v>20.799528123124979</v>
       </c>
       <c r="F56" s="0">
-        <v>0.27784861733985622</v>
+        <v>0.29952812312497912</v>
       </c>
       <c r="G56" s="0">
-        <v>0.27784861733985622</v>
+        <v>0.29952812312497912</v>
       </c>
       <c r="H56" s="0">
-        <v>20.277848617339856</v>
+        <v>20.299528123124979</v>
       </c>
       <c r="I56" s="0">
-        <v>-0.22215138266014378</v>
+        <v>-0.20047187687502088</v>
       </c>
       <c r="J56" s="0">
-        <v>0.22215138266014378</v>
+        <v>0.20047187687502088</v>
       </c>
       <c r="K56" s="0" t="b">
         <v>0</v>
@@ -2913,28 +2913,28 @@
         <v>69</v>
       </c>
       <c r="C57" s="0">
-        <v>632.78740000000005</v>
+        <v>647.98350000000005</v>
       </c>
       <c r="D57" s="0">
         <v>21</v>
       </c>
       <c r="E57" s="0">
-        <v>21.065989215691644</v>
+        <v>20.836202731495163</v>
       </c>
       <c r="F57" s="0">
-        <v>0.065989215691644176</v>
+        <v>-0.16379726850483678</v>
       </c>
       <c r="G57" s="0">
-        <v>0.065989215691644176</v>
+        <v>0.16379726850483678</v>
       </c>
       <c r="H57" s="0">
-        <v>20.565989215691644</v>
+        <v>20.336202731495163</v>
       </c>
       <c r="I57" s="0">
-        <v>-0.43401078430835582</v>
+        <v>-0.66379726850483678</v>
       </c>
       <c r="J57" s="0">
-        <v>0.43401078430835582</v>
+        <v>0.66379726850483678</v>
       </c>
       <c r="K57" s="0" t="b">
         <v>0</v>
@@ -2957,28 +2957,28 @@
         <v>69</v>
       </c>
       <c r="C58" s="0">
-        <v>1105.7334000000001</v>
+        <v>1095.0534</v>
       </c>
       <c r="D58" s="0">
         <v>23.5</v>
       </c>
       <c r="E58" s="0">
-        <v>21.042413904615138</v>
+        <v>21.052096407776137</v>
       </c>
       <c r="F58" s="0">
-        <v>-2.4575860953848618</v>
+        <v>-2.447903592223863</v>
       </c>
       <c r="G58" s="0">
-        <v>2.4575860953848618</v>
+        <v>2.447903592223863</v>
       </c>
       <c r="H58" s="0">
-        <v>20.542413904615138</v>
+        <v>20.552096407776137</v>
       </c>
       <c r="I58" s="0">
-        <v>-2.9575860953848618</v>
+        <v>-2.947903592223863</v>
       </c>
       <c r="J58" s="0">
-        <v>2.9575860953848618</v>
+        <v>2.947903592223863</v>
       </c>
       <c r="K58" s="0" t="b">
         <v>0</v>
@@ -3001,28 +3001,28 @@
         <v>69</v>
       </c>
       <c r="C59" s="0">
-        <v>665.27829999999995</v>
+        <v>672.01580000000001</v>
       </c>
       <c r="D59" s="0">
         <v>20.5</v>
       </c>
       <c r="E59" s="0">
-        <v>21.315954637397805</v>
+        <v>21.320458118345375</v>
       </c>
       <c r="F59" s="0">
-        <v>0.81595463739780527</v>
+        <v>0.82045811834537474</v>
       </c>
       <c r="G59" s="0">
-        <v>0.81595463739780527</v>
+        <v>0.82045811834537474</v>
       </c>
       <c r="H59" s="0">
-        <v>20.815954637397805</v>
+        <v>20.820458118345375</v>
       </c>
       <c r="I59" s="0">
-        <v>0.31595463739780527</v>
+        <v>0.32045811834537474</v>
       </c>
       <c r="J59" s="0">
-        <v>0.31595463739780527</v>
+        <v>0.32045811834537474</v>
       </c>
       <c r="K59" s="0" t="b">
         <v>1</v>
@@ -3045,28 +3045,28 @@
         <v>69</v>
       </c>
       <c r="C60" s="0">
-        <v>655.14710000000002</v>
+        <v>697.428</v>
       </c>
       <c r="D60" s="0">
         <v>21.5</v>
       </c>
       <c r="E60" s="0">
-        <v>20.9841619381891</v>
+        <v>20.775603121551047</v>
       </c>
       <c r="F60" s="0">
-        <v>-0.51583806181089997</v>
+        <v>-0.72439687844895318</v>
       </c>
       <c r="G60" s="0">
-        <v>0.51583806181089997</v>
+        <v>0.72439687844895318</v>
       </c>
       <c r="H60" s="0">
-        <v>20.4841619381891</v>
+        <v>20.275603121551047</v>
       </c>
       <c r="I60" s="0">
-        <v>-1.0158380618109</v>
+        <v>-1.2243968784489532</v>
       </c>
       <c r="J60" s="0">
-        <v>1.0158380618109</v>
+        <v>1.2243968784489532</v>
       </c>
       <c r="K60" s="0" t="b">
         <v>0</v>
@@ -3089,28 +3089,28 @@
         <v>69</v>
       </c>
       <c r="C61" s="0">
-        <v>642.19590000000005</v>
+        <v>648.5258</v>
       </c>
       <c r="D61" s="0">
         <v>20</v>
       </c>
       <c r="E61" s="0">
-        <v>21.041706676248435</v>
+        <v>20.97582247569229</v>
       </c>
       <c r="F61" s="0">
-        <v>1.0417066762484346</v>
+        <v>0.97582247569228997</v>
       </c>
       <c r="G61" s="0">
-        <v>1.0417066762484346</v>
+        <v>0.97582247569228997</v>
       </c>
       <c r="H61" s="0">
-        <v>20.541706676248435</v>
+        <v>20.47582247569229</v>
       </c>
       <c r="I61" s="0">
-        <v>0.54170667624843461</v>
+        <v>0.47582247569228997</v>
       </c>
       <c r="J61" s="0">
-        <v>0.54170667624843461</v>
+        <v>0.47582247569228997</v>
       </c>
       <c r="K61" s="0" t="b">
         <v>1</v>
@@ -3133,28 +3133,28 @@
         <v>69</v>
       </c>
       <c r="C62" s="0">
-        <v>671.02829999999995</v>
+        <v>690.99220000000003</v>
       </c>
       <c r="D62" s="0">
         <v>23</v>
       </c>
       <c r="E62" s="0">
-        <v>21.041842687338736</v>
+        <v>20.989710323151197</v>
       </c>
       <c r="F62" s="0">
-        <v>-1.9581573126612639</v>
+        <v>-2.010289676848803</v>
       </c>
       <c r="G62" s="0">
-        <v>1.9581573126612639</v>
+        <v>2.010289676848803</v>
       </c>
       <c r="H62" s="0">
-        <v>20.541842687338736</v>
+        <v>20.489710323151197</v>
       </c>
       <c r="I62" s="0">
-        <v>-2.4581573126612639</v>
+        <v>-2.510289676848803</v>
       </c>
       <c r="J62" s="0">
-        <v>2.4581573126612639</v>
+        <v>2.510289676848803</v>
       </c>
       <c r="K62" s="0" t="b">
         <v>0</v>
@@ -3177,28 +3177,28 @@
         <v>69</v>
       </c>
       <c r="C63" s="0">
-        <v>658.74609999999996</v>
+        <v>674.3954</v>
       </c>
       <c r="D63" s="0">
         <v>21.5</v>
       </c>
       <c r="E63" s="0">
-        <v>21.102922757856305</v>
+        <v>21.075287253420708</v>
       </c>
       <c r="F63" s="0">
-        <v>-0.39707724214369478</v>
+        <v>-0.42471274657929215</v>
       </c>
       <c r="G63" s="0">
-        <v>0.39707724214369478</v>
+        <v>0.42471274657929215</v>
       </c>
       <c r="H63" s="0">
-        <v>20.602922757856305</v>
+        <v>20.575287253420708</v>
       </c>
       <c r="I63" s="0">
-        <v>-0.89707724214369478</v>
+        <v>-0.92471274657929215</v>
       </c>
       <c r="J63" s="0">
-        <v>0.89707724214369478</v>
+        <v>0.92471274657929215</v>
       </c>
       <c r="K63" s="0" t="b">
         <v>0</v>
@@ -3221,28 +3221,28 @@
         <v>69</v>
       </c>
       <c r="C64" s="0">
-        <v>418.81540000000001</v>
+        <v>427.42320000000001</v>
       </c>
       <c r="D64" s="0">
         <v>22.5</v>
       </c>
       <c r="E64" s="0">
-        <v>20.987135162311674</v>
+        <v>20.814400317136649</v>
       </c>
       <c r="F64" s="0">
-        <v>-1.5128648376883263</v>
+        <v>-1.6855996828633515</v>
       </c>
       <c r="G64" s="0">
-        <v>1.5128648376883263</v>
+        <v>1.6855996828633515</v>
       </c>
       <c r="H64" s="0">
-        <v>20.487135162311674</v>
+        <v>20.314400317136649</v>
       </c>
       <c r="I64" s="0">
-        <v>-2.0128648376883263</v>
+        <v>-2.1855996828633515</v>
       </c>
       <c r="J64" s="0">
-        <v>2.0128648376883263</v>
+        <v>2.1855996828633515</v>
       </c>
       <c r="K64" s="0" t="b">
         <v>0</v>
@@ -3265,28 +3265,28 @@
         <v>69</v>
       </c>
       <c r="C65" s="0">
-        <v>593.42259999999999</v>
+        <v>597.84789999999998</v>
       </c>
       <c r="D65" s="0">
         <v>19.25</v>
       </c>
       <c r="E65" s="0">
-        <v>21.166861627534502</v>
+        <v>21.257513888267084</v>
       </c>
       <c r="F65" s="0">
-        <v>1.9168616275345016</v>
+        <v>2.0075138882670842</v>
       </c>
       <c r="G65" s="0">
-        <v>1.9168616275345016</v>
+        <v>2.0075138882670842</v>
       </c>
       <c r="H65" s="0">
-        <v>20.666861627534502</v>
+        <v>20.757513888267084</v>
       </c>
       <c r="I65" s="0">
-        <v>1.4168616275345016</v>
+        <v>1.5075138882670842</v>
       </c>
       <c r="J65" s="0">
-        <v>1.4168616275345016</v>
+        <v>1.5075138882670842</v>
       </c>
       <c r="K65" s="0" t="b">
         <v>1</v>
@@ -3309,28 +3309,28 @@
         <v>69</v>
       </c>
       <c r="C66" s="0">
-        <v>709.44029999999998</v>
+        <v>710.17049999999995</v>
       </c>
       <c r="D66" s="0">
         <v>23.5</v>
       </c>
       <c r="E66" s="0">
-        <v>21.048236627444428</v>
+        <v>20.834972246805379</v>
       </c>
       <c r="F66" s="0">
-        <v>-2.4517633725555719</v>
+        <v>-2.6650277531946216</v>
       </c>
       <c r="G66" s="0">
-        <v>2.4517633725555719</v>
+        <v>2.6650277531946216</v>
       </c>
       <c r="H66" s="0">
-        <v>20.548236627444428</v>
+        <v>20.334972246805379</v>
       </c>
       <c r="I66" s="0">
-        <v>-2.9517633725555719</v>
+        <v>-3.1650277531946216</v>
       </c>
       <c r="J66" s="0">
-        <v>2.9517633725555719</v>
+        <v>3.1650277531946216</v>
       </c>
       <c r="K66" s="0" t="b">
         <v>0</v>
@@ -3353,28 +3353,28 @@
         <v>69</v>
       </c>
       <c r="C67" s="0">
-        <v>625.83199999999999</v>
+        <v>639.05380000000002</v>
       </c>
       <c r="D67" s="0">
         <v>21.5</v>
       </c>
       <c r="E67" s="0">
-        <v>21.046739821717004</v>
+        <v>20.834976157062499</v>
       </c>
       <c r="F67" s="0">
-        <v>-0.4532601782829957</v>
+        <v>-0.66502384293750083</v>
       </c>
       <c r="G67" s="0">
-        <v>0.4532601782829957</v>
+        <v>0.66502384293750083</v>
       </c>
       <c r="H67" s="0">
-        <v>20.546739821717004</v>
+        <v>20.334976157062499</v>
       </c>
       <c r="I67" s="0">
-        <v>-0.9532601782829957</v>
+        <v>-1.1650238429375008</v>
       </c>
       <c r="J67" s="0">
-        <v>0.9532601782829957</v>
+        <v>1.1650238429375008</v>
       </c>
       <c r="K67" s="0" t="b">
         <v>0</v>
@@ -3397,28 +3397,28 @@
         <v>69</v>
       </c>
       <c r="C68" s="0">
-        <v>889.9828</v>
+        <v>892.07839999999999</v>
       </c>
       <c r="D68" s="0">
         <v>19</v>
       </c>
       <c r="E68" s="0">
-        <v>21.075592832838694</v>
+        <v>20.857945763204846</v>
       </c>
       <c r="F68" s="0">
-        <v>2.0755928328386943</v>
+        <v>1.857945763204846</v>
       </c>
       <c r="G68" s="0">
-        <v>2.0755928328386943</v>
+        <v>1.857945763204846</v>
       </c>
       <c r="H68" s="0">
-        <v>20.575592832838694</v>
+        <v>20.357945763204846</v>
       </c>
       <c r="I68" s="0">
-        <v>1.5755928328386943</v>
+        <v>1.3579457632048459</v>
       </c>
       <c r="J68" s="0">
-        <v>1.5755928328386943</v>
+        <v>1.3579457632048459</v>
       </c>
       <c r="K68" s="0" t="b">
         <v>1</v>
@@ -3479,16 +3479,16 @@
         <v>85</v>
       </c>
       <c r="B2" s="0">
-        <v>1.494</v>
+        <v>1.4970000000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>1.8500000000000001</v>
+        <v>1.853</v>
       </c>
       <c r="D2" s="0">
-        <v>0.035000000000000003</v>
+        <v>0.035999999999999997</v>
       </c>
       <c r="E2" s="0">
-        <v>0.042999999999999997</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="F2" s="0"/>
       <c r="G2" s="0"/>
@@ -3501,19 +3501,19 @@
         <v>0.014</v>
       </c>
       <c r="C3" s="0">
-        <v>0.023</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.014</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="E3" s="0">
-        <v>0.035999999999999997</v>
+        <v>0.037999999999999999</v>
       </c>
       <c r="F3" s="0">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G3" s="0">
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3532,18 +3532,18 @@
         <v>88</v>
       </c>
       <c r="B5" s="0">
-        <v>1.5069999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
       <c r="E5" s="0">
-        <v>-0.45700000000000002</v>
+        <v>-0.45500000000000002</v>
       </c>
       <c r="F5" s="0">
-        <v>38.200000000000003</v>
+        <v>38.399999999999999</v>
       </c>
       <c r="G5" s="0">
-        <v>44</v>
+        <v>43.899999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -3570,7 +3570,7 @@
         <v>90</v>
       </c>
       <c r="B7" s="0">
-        <v>1.575</v>
+        <v>1.5760000000000001</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -3663,7 +3663,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="true"/>
-    <col min="2" max="2" width="7.42578125" customWidth="true"/>
+    <col min="2" max="2" width="7.7109375" customWidth="true"/>
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
     <col min="5" max="5" width="6.7109375" customWidth="true"/>
@@ -3691,13 +3691,13 @@
         <v>112</v>
       </c>
       <c r="B2" s="0">
-        <v>21.355</v>
+        <v>21.344899999999999</v>
       </c>
       <c r="C2" s="0">
-        <v>0.82020000000000004</v>
+        <v>0.82069999999999999</v>
       </c>
       <c r="D2" s="0">
-        <v>26.035</v>
+        <v>26.007000000000001</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
@@ -3714,10 +3714,10 @@
         <v>0.00069999999999999999</v>
       </c>
       <c r="D3" s="0">
-        <v>0.55600000000000005</v>
+        <v>0.57299999999999995</v>
       </c>
       <c r="E3" s="0">
-        <v>0.57989999999999997</v>
+        <v>0.56850000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -3725,16 +3725,16 @@
         <v>114</v>
       </c>
       <c r="B4" s="0">
-        <v>-0.021600000000000001</v>
+        <v>-0.021700000000000001</v>
       </c>
       <c r="C4" s="0">
         <v>0.013299999999999999</v>
       </c>
       <c r="D4" s="0">
-        <v>-1.629</v>
+        <v>-1.631</v>
       </c>
       <c r="E4" s="0">
-        <v>0.10829999999999999</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="5">
@@ -3742,16 +3742,16 @@
         <v>115</v>
       </c>
       <c r="B5" s="0">
-        <v>0.54559999999999997</v>
+        <v>0.54590000000000005</v>
       </c>
       <c r="C5" s="0">
-        <v>0.45450000000000002</v>
+        <v>0.45419999999999999</v>
       </c>
       <c r="D5" s="0">
-        <v>1.2010000000000001</v>
+        <v>1.202</v>
       </c>
       <c r="E5" s="0">
-        <v>0.2344</v>
+        <v>0.23400000000000001</v>
       </c>
     </row>
   </sheetData>
